--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/16-horas-por-caso.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/16-horas-por-caso.xlsx
@@ -74,6 +74,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00B0A6C4"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="003B1F5E"/>
       <sz val="9"/>
@@ -107,11 +112,6 @@
       <b val="1"/>
       <color rgb="003B1F5E"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00B0A6C4"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -212,29 +212,29 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -243,13 +243,13 @@
     <xf numFmtId="9" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -273,7 +273,7 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -292,7 +292,7 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1060,17 +1060,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1184,7 +1196,7 @@
       </c>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="20">
-        <f>COUNTIF($L$32:$L$91,"Consome mais do que paga")</f>
+        <f>COUNTIF(Casos!$M$5:$M$204,"Consome mais do que paga")</f>
         <v>0</v>
       </c>
       <c r="L5" s="14" t="n"/>
@@ -5778,7 +5790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5790,6 +5802,9 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5852,6 +5867,21 @@
           <t>Fase</t>
         </is>
       </c>
+      <c r="K4" s="39" t="inlineStr">
+        <is>
+          <t>(horas gastas)</t>
+        </is>
+      </c>
+      <c r="L4" s="39" t="inlineStr">
+        <is>
+          <t>(custo)</t>
+        </is>
+      </c>
+      <c r="M4" s="39" t="inlineStr">
+        <is>
+          <t>(situação)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="41" t="inlineStr">
@@ -5893,6 +5923,18 @@
           <t>Consultivo</t>
         </is>
       </c>
+      <c r="K5" s="39">
+        <f>IF(A5="","",N(H5)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A5))</f>
+        <v>16</v>
+      </c>
+      <c r="L5" s="39">
+        <f>IF(A5="","",N(H5)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A5))</f>
+        <v>1150.77922077922</v>
+      </c>
+      <c r="M5" s="39" t="str">
+        <f>IF(A5="","",IF(E5="Interno","Interno",IF(K5=0,"Sem horas",IF(L5&gt;N(F5),"Consome mais do que paga",IF(AND(N(G5)&gt;0,K5/G5&gt;1),"Estourou as horas",IF(AND(N(F5)&gt;0,(F5-L5)/F5&lt;0.2),"Margem baixa",IF(AND(N(G5)&gt;0,K5/G5&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="41" t="inlineStr">
@@ -5934,6 +5976,18 @@
           <t>Inicial</t>
         </is>
       </c>
+      <c r="K6" s="39">
+        <f>IF(A6="","",N(H6)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A6))</f>
+        <v>22</v>
+      </c>
+      <c r="L6" s="39">
+        <f>IF(A6="","",N(H6)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A6))</f>
+        <v>1538.29004329004</v>
+      </c>
+      <c r="M6" s="39" t="str">
+        <f>IF(A6="","",IF(E6="Interno","Interno",IF(K6=0,"Sem horas",IF(L6&gt;N(F6),"Consome mais do que paga",IF(AND(N(G6)&gt;0,K6/G6&gt;1),"Estourou as horas",IF(AND(N(F6)&gt;0,(F6-L6)/F6&lt;0.2),"Margem baixa",IF(AND(N(G6)&gt;0,K6/G6&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="41" t="inlineStr">
@@ -5975,6 +6029,18 @@
           <t>Inicial</t>
         </is>
       </c>
+      <c r="K7" s="39">
+        <f>IF(A7="","",N(H7)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A7))</f>
+        <v>34</v>
+      </c>
+      <c r="L7" s="39">
+        <f>IF(A7="","",N(H7)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A7))</f>
+        <v>2099.28571428571</v>
+      </c>
+      <c r="M7" s="39" t="str">
+        <f>IF(A7="","",IF(E7="Interno","Interno",IF(K7=0,"Sem horas",IF(L7&gt;N(F7),"Consome mais do que paga",IF(AND(N(G7)&gt;0,K7/G7&gt;1),"Estourou as horas",IF(AND(N(F7)&gt;0,(F7-L7)/F7&lt;0.2),"Margem baixa",IF(AND(N(G7)&gt;0,K7/G7&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="41" t="inlineStr">
@@ -6016,6 +6082,18 @@
           <t>Inicial</t>
         </is>
       </c>
+      <c r="K8" s="39">
+        <f>IF(A8="","",N(H8)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A8))</f>
+        <v>15</v>
+      </c>
+      <c r="L8" s="39">
+        <f>IF(A8="","",N(H8)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A8))</f>
+        <v>1028.97186147186</v>
+      </c>
+      <c r="M8" s="39" t="str">
+        <f>IF(A8="","",IF(E8="Interno","Interno",IF(K8=0,"Sem horas",IF(L8&gt;N(F8),"Consome mais do que paga",IF(AND(N(G8)&gt;0,K8/G8&gt;1),"Estourou as horas",IF(AND(N(F8)&gt;0,(F8-L8)/F8&lt;0.2),"Margem baixa",IF(AND(N(G8)&gt;0,K8/G8&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="41" t="inlineStr">
@@ -6057,6 +6135,18 @@
           <t>Consultivo</t>
         </is>
       </c>
+      <c r="K9" s="39">
+        <f>IF(A9="","",N(H9)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A9))</f>
+        <v>24</v>
+      </c>
+      <c r="L9" s="39">
+        <f>IF(A9="","",N(H9)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A9))</f>
+        <v>1746.23376623377</v>
+      </c>
+      <c r="M9" s="39" t="str">
+        <f>IF(A9="","",IF(E9="Interno","Interno",IF(K9=0,"Sem horas",IF(L9&gt;N(F9),"Consome mais do que paga",IF(AND(N(G9)&gt;0,K9/G9&gt;1),"Estourou as horas",IF(AND(N(F9)&gt;0,(F9-L9)/F9&lt;0.2),"Margem baixa",IF(AND(N(G9)&gt;0,K9/G9&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="41" t="inlineStr">
@@ -6098,6 +6188,18 @@
           <t>Consultivo</t>
         </is>
       </c>
+      <c r="K10" s="39">
+        <f>IF(A10="","",N(H10)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A10))</f>
+        <v>16</v>
+      </c>
+      <c r="L10" s="39">
+        <f>IF(A10="","",N(H10)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A10))</f>
+        <v>992.489177489178</v>
+      </c>
+      <c r="M10" s="39" t="str">
+        <f>IF(A10="","",IF(E10="Interno","Interno",IF(K10=0,"Sem horas",IF(L10&gt;N(F10),"Consome mais do que paga",IF(AND(N(G10)&gt;0,K10/G10&gt;1),"Estourou as horas",IF(AND(N(F10)&gt;0,(F10-L10)/F10&lt;0.2),"Margem baixa",IF(AND(N(G10)&gt;0,K10/G10&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="41" t="inlineStr">
@@ -6139,6 +6241,18 @@
           <t>Consultivo</t>
         </is>
       </c>
+      <c r="K11" s="39">
+        <f>IF(A11="","",N(H11)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A11))</f>
+        <v>9</v>
+      </c>
+      <c r="L11" s="39">
+        <f>IF(A11="","",N(H11)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A11))</f>
+        <v>545.595238095238</v>
+      </c>
+      <c r="M11" s="39" t="str">
+        <f>IF(A11="","",IF(E11="Interno","Interno",IF(K11=0,"Sem horas",IF(L11&gt;N(F11),"Consome mais do que paga",IF(AND(N(G11)&gt;0,K11/G11&gt;1),"Estourou as horas",IF(AND(N(F11)&gt;0,(F11-L11)/F11&lt;0.2),"Margem baixa",IF(AND(N(G11)&gt;0,K11/G11&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="41" t="inlineStr">
@@ -6180,6 +6294,18 @@
           <t>Instrução</t>
         </is>
       </c>
+      <c r="K12" s="39">
+        <f>IF(A12="","",N(H12)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A12))</f>
+        <v>70</v>
+      </c>
+      <c r="L12" s="39">
+        <f>IF(A12="","",N(H12)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A12))</f>
+        <v>4580.41125541126</v>
+      </c>
+      <c r="M12" s="39" t="str">
+        <f>IF(A12="","",IF(E12="Interno","Interno",IF(K12=0,"Sem horas",IF(L12&gt;N(F12),"Consome mais do que paga",IF(AND(N(G12)&gt;0,K12/G12&gt;1),"Estourou as horas",IF(AND(N(F12)&gt;0,(F12-L12)/F12&lt;0.2),"Margem baixa",IF(AND(N(G12)&gt;0,K12/G12&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="41" t="inlineStr">
@@ -6221,6 +6347,18 @@
           <t>Execução</t>
         </is>
       </c>
+      <c r="K13" s="39">
+        <f>IF(A13="","",N(H13)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A13))</f>
+        <v>50</v>
+      </c>
+      <c r="L13" s="39">
+        <f>IF(A13="","",N(H13)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A13))</f>
+        <v>3313.6038961039</v>
+      </c>
+      <c r="M13" s="39" t="str">
+        <f>IF(A13="","",IF(E13="Interno","Interno",IF(K13=0,"Sem horas",IF(L13&gt;N(F13),"Consome mais do que paga",IF(AND(N(G13)&gt;0,K13/G13&gt;1),"Estourou as horas",IF(AND(N(F13)&gt;0,(F13-L13)/F13&lt;0.2),"Margem baixa",IF(AND(N(G13)&gt;0,K13/G13&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="41" t="inlineStr">
@@ -6262,6 +6400,18 @@
           <t>Sentença</t>
         </is>
       </c>
+      <c r="K14" s="39">
+        <f>IF(A14="","",N(H14)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A14))</f>
+        <v>88</v>
+      </c>
+      <c r="L14" s="39">
+        <f>IF(A14="","",N(H14)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A14))</f>
+        <v>5717.30519480519</v>
+      </c>
+      <c r="M14" s="39" t="str">
+        <f>IF(A14="","",IF(E14="Interno","Interno",IF(K14=0,"Sem horas",IF(L14&gt;N(F14),"Consome mais do que paga",IF(AND(N(G14)&gt;0,K14/G14&gt;1),"Estourou as horas",IF(AND(N(F14)&gt;0,(F14-L14)/F14&lt;0.2),"Margem baixa",IF(AND(N(G14)&gt;0,K14/G14&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="41" t="inlineStr">
@@ -6303,6 +6453,18 @@
           <t>Recurso</t>
         </is>
       </c>
+      <c r="K15" s="39">
+        <f>IF(A15="","",N(H15)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A15))</f>
+        <v>48</v>
+      </c>
+      <c r="L15" s="39">
+        <f>IF(A15="","",N(H15)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A15))</f>
+        <v>2973.00865800866</v>
+      </c>
+      <c r="M15" s="39" t="str">
+        <f>IF(A15="","",IF(E15="Interno","Interno",IF(K15=0,"Sem horas",IF(L15&gt;N(F15),"Consome mais do que paga",IF(AND(N(G15)&gt;0,K15/G15&gt;1),"Estourou as horas",IF(AND(N(F15)&gt;0,(F15-L15)/F15&lt;0.2),"Margem baixa",IF(AND(N(G15)&gt;0,K15/G15&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="inlineStr">
@@ -6344,6 +6506,18 @@
           <t>Consultivo</t>
         </is>
       </c>
+      <c r="K16" s="39">
+        <f>IF(A16="","",N(H16)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A16))</f>
+        <v>107</v>
+      </c>
+      <c r="L16" s="39">
+        <f>IF(A16="","",N(H16)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A16))</f>
+        <v>7223.47402597403</v>
+      </c>
+      <c r="M16" s="39" t="str">
+        <f>IF(A16="","",IF(E16="Interno","Interno",IF(K16=0,"Sem horas",IF(L16&gt;N(F16),"Consome mais do que paga",IF(AND(N(G16)&gt;0,K16/G16&gt;1),"Estourou as horas",IF(AND(N(F16)&gt;0,(F16-L16)/F16&lt;0.2),"Margem baixa",IF(AND(N(G16)&gt;0,K16/G16&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="41" t="inlineStr">
@@ -6385,6 +6559,18 @@
           <t>Inicial</t>
         </is>
       </c>
+      <c r="K17" s="39">
+        <f>IF(A17="","",N(H17)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A17))</f>
+        <v>45</v>
+      </c>
+      <c r="L17" s="39">
+        <f>IF(A17="","",N(H17)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A17))</f>
+        <v>3018.91774891775</v>
+      </c>
+      <c r="M17" s="39" t="str">
+        <f>IF(A17="","",IF(E17="Interno","Interno",IF(K17=0,"Sem horas",IF(L17&gt;N(F17),"Consome mais do que paga",IF(AND(N(G17)&gt;0,K17/G17&gt;1),"Estourou as horas",IF(AND(N(F17)&gt;0,(F17-L17)/F17&lt;0.2),"Margem baixa",IF(AND(N(G17)&gt;0,K17/G17&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="41" t="inlineStr">
@@ -6426,6 +6612,18 @@
           <t>Instrução</t>
         </is>
       </c>
+      <c r="K18" s="39">
+        <f>IF(A18="","",N(H18)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A18))</f>
+        <v>78</v>
+      </c>
+      <c r="L18" s="39">
+        <f>IF(A18="","",N(H18)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A18))</f>
+        <v>5180.32467532468</v>
+      </c>
+      <c r="M18" s="39" t="str">
+        <f>IF(A18="","",IF(E18="Interno","Interno",IF(K18=0,"Sem horas",IF(L18&gt;N(F18),"Consome mais do que paga",IF(AND(N(G18)&gt;0,K18/G18&gt;1),"Estourou as horas",IF(AND(N(F18)&gt;0,(F18-L18)/F18&lt;0.2),"Margem baixa",IF(AND(N(G18)&gt;0,K18/G18&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="41" t="inlineStr">
@@ -6467,6 +6665,18 @@
           <t>Inicial</t>
         </is>
       </c>
+      <c r="K19" s="39">
+        <f>IF(A19="","",N(H19)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A19))</f>
+        <v>30</v>
+      </c>
+      <c r="L19" s="39">
+        <f>IF(A19="","",N(H19)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A19))</f>
+        <v>1850.60606060606</v>
+      </c>
+      <c r="M19" s="39" t="str">
+        <f>IF(A19="","",IF(E19="Interno","Interno",IF(K19=0,"Sem horas",IF(L19&gt;N(F19),"Consome mais do que paga",IF(AND(N(G19)&gt;0,K19/G19&gt;1),"Estourou as horas",IF(AND(N(F19)&gt;0,(F19-L19)/F19&lt;0.2),"Margem baixa",IF(AND(N(G19)&gt;0,K19/G19&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
@@ -6508,6 +6718,18 @@
           <t>Consultivo</t>
         </is>
       </c>
+      <c r="K20" s="39">
+        <f>IF(A20="","",N(H20)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A20))</f>
+        <v>24</v>
+      </c>
+      <c r="L20" s="39">
+        <f>IF(A20="","",N(H20)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A20))</f>
+        <v>1574.5670995671</v>
+      </c>
+      <c r="M20" s="39" t="str">
+        <f>IF(A20="","",IF(E20="Interno","Interno",IF(K20=0,"Sem horas",IF(L20&gt;N(F20),"Consome mais do que paga",IF(AND(N(G20)&gt;0,K20/G20&gt;1),"Estourou as horas",IF(AND(N(F20)&gt;0,(F20-L20)/F20&lt;0.2),"Margem baixa",IF(AND(N(G20)&gt;0,K20/G20&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="41" t="inlineStr">
@@ -6549,6 +6771,18 @@
           <t>Acordo</t>
         </is>
       </c>
+      <c r="K21" s="39">
+        <f>IF(A21="","",N(H21)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A21))</f>
+        <v>48</v>
+      </c>
+      <c r="L21" s="39">
+        <f>IF(A21="","",N(H21)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A21))</f>
+        <v>3101.2012987013</v>
+      </c>
+      <c r="M21" s="39" t="str">
+        <f>IF(A21="","",IF(E21="Interno","Interno",IF(K21=0,"Sem horas",IF(L21&gt;N(F21),"Consome mais do que paga",IF(AND(N(G21)&gt;0,K21/G21&gt;1),"Estourou as horas",IF(AND(N(F21)&gt;0,(F21-L21)/F21&lt;0.2),"Margem baixa",IF(AND(N(G21)&gt;0,K21/G21&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="41" t="inlineStr">
@@ -6590,6 +6824,18 @@
           <t>Execução</t>
         </is>
       </c>
+      <c r="K22" s="39">
+        <f>IF(A22="","",N(H22)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A22))</f>
+        <v>33</v>
+      </c>
+      <c r="L22" s="39">
+        <f>IF(A22="","",N(H22)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A22))</f>
+        <v>2049.93506493507</v>
+      </c>
+      <c r="M22" s="39" t="str">
+        <f>IF(A22="","",IF(E22="Interno","Interno",IF(K22=0,"Sem horas",IF(L22&gt;N(F22),"Consome mais do que paga",IF(AND(N(G22)&gt;0,K22/G22&gt;1),"Estourou as horas",IF(AND(N(F22)&gt;0,(F22-L22)/F22&lt;0.2),"Margem baixa",IF(AND(N(G22)&gt;0,K22/G22&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="41" t="inlineStr">
@@ -6631,6 +6877,18 @@
           <t>Sentença</t>
         </is>
       </c>
+      <c r="K23" s="39">
+        <f>IF(A23="","",N(H23)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A23))</f>
+        <v>100</v>
+      </c>
+      <c r="L23" s="39">
+        <f>IF(A23="","",N(H23)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A23))</f>
+        <v>6647.27272727273</v>
+      </c>
+      <c r="M23" s="39" t="str">
+        <f>IF(A23="","",IF(E23="Interno","Interno",IF(K23=0,"Sem horas",IF(L23&gt;N(F23),"Consome mais do que paga",IF(AND(N(G23)&gt;0,K23/G23&gt;1),"Estourou as horas",IF(AND(N(F23)&gt;0,(F23-L23)/F23&lt;0.2),"Margem baixa",IF(AND(N(G23)&gt;0,K23/G23&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="41" t="inlineStr">
@@ -6672,6 +6930,18 @@
           <t>Instrução</t>
         </is>
       </c>
+      <c r="K24" s="39">
+        <f>IF(A24="","",N(H24)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A24))</f>
+        <v>30</v>
+      </c>
+      <c r="L24" s="39">
+        <f>IF(A24="","",N(H24)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A24))</f>
+        <v>1851.72077922078</v>
+      </c>
+      <c r="M24" s="39" t="str">
+        <f>IF(A24="","",IF(E24="Interno","Interno",IF(K24=0,"Sem horas",IF(L24&gt;N(F24),"Consome mais do que paga",IF(AND(N(G24)&gt;0,K24/G24&gt;1),"Estourou as horas",IF(AND(N(F24)&gt;0,(F24-L24)/F24&lt;0.2),"Margem baixa",IF(AND(N(G24)&gt;0,K24/G24&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="41" t="inlineStr">
@@ -6713,6 +6983,18 @@
           <t>Instrução</t>
         </is>
       </c>
+      <c r="K25" s="39">
+        <f>IF(A25="","",N(H25)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A25))</f>
+        <v>86</v>
+      </c>
+      <c r="L25" s="39">
+        <f>IF(A25="","",N(H25)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A25))</f>
+        <v>5684.37229437229</v>
+      </c>
+      <c r="M25" s="39" t="str">
+        <f>IF(A25="","",IF(E25="Interno","Interno",IF(K25=0,"Sem horas",IF(L25&gt;N(F25),"Consome mais do que paga",IF(AND(N(G25)&gt;0,K25/G25&gt;1),"Estourou as horas",IF(AND(N(F25)&gt;0,(F25-L25)/F25&lt;0.2),"Margem baixa",IF(AND(N(G25)&gt;0,K25/G25&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="41" t="inlineStr">
@@ -6754,6 +7036,18 @@
           <t>Inicial</t>
         </is>
       </c>
+      <c r="K26" s="39">
+        <f>IF(A26="","",N(H26)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A26))</f>
+        <v>27</v>
+      </c>
+      <c r="L26" s="39">
+        <f>IF(A26="","",N(H26)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A26))</f>
+        <v>1751.60173160173</v>
+      </c>
+      <c r="M26" s="39" t="str">
+        <f>IF(A26="","",IF(E26="Interno","Interno",IF(K26=0,"Sem horas",IF(L26&gt;N(F26),"Consome mais do que paga",IF(AND(N(G26)&gt;0,K26/G26&gt;1),"Estourou as horas",IF(AND(N(F26)&gt;0,(F26-L26)/F26&lt;0.2),"Margem baixa",IF(AND(N(G26)&gt;0,K26/G26&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="41" t="inlineStr">
@@ -6795,6 +7089,18 @@
           <t>Inicial</t>
         </is>
       </c>
+      <c r="K27" s="39">
+        <f>IF(A27="","",N(H27)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A27))</f>
+        <v>45</v>
+      </c>
+      <c r="L27" s="39">
+        <f>IF(A27="","",N(H27)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A27))</f>
+        <v>2841.67748917749</v>
+      </c>
+      <c r="M27" s="39" t="str">
+        <f>IF(A27="","",IF(E27="Interno","Interno",IF(K27=0,"Sem horas",IF(L27&gt;N(F27),"Consome mais do que paga",IF(AND(N(G27)&gt;0,K27/G27&gt;1),"Estourou as horas",IF(AND(N(F27)&gt;0,(F27-L27)/F27&lt;0.2),"Margem baixa",IF(AND(N(G27)&gt;0,K27/G27&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="41" t="inlineStr">
@@ -6836,6 +7142,18 @@
           <t>Acordo</t>
         </is>
       </c>
+      <c r="K28" s="39">
+        <f>IF(A28="","",N(H28)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A28))</f>
+        <v>34</v>
+      </c>
+      <c r="L28" s="39">
+        <f>IF(A28="","",N(H28)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A28))</f>
+        <v>2103.74458874459</v>
+      </c>
+      <c r="M28" s="39" t="str">
+        <f>IF(A28="","",IF(E28="Interno","Interno",IF(K28=0,"Sem horas",IF(L28&gt;N(F28),"Consome mais do que paga",IF(AND(N(G28)&gt;0,K28/G28&gt;1),"Estourou as horas",IF(AND(N(F28)&gt;0,(F28-L28)/F28&lt;0.2),"Margem baixa",IF(AND(N(G28)&gt;0,K28/G28&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="41" t="inlineStr">
@@ -6877,6 +7195,18 @@
           <t>Recurso</t>
         </is>
       </c>
+      <c r="K29" s="39">
+        <f>IF(A29="","",N(H29)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A29))</f>
+        <v>126</v>
+      </c>
+      <c r="L29" s="39">
+        <f>IF(A29="","",N(H29)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A29))</f>
+        <v>8525.64935064935</v>
+      </c>
+      <c r="M29" s="39" t="str">
+        <f>IF(A29="","",IF(E29="Interno","Interno",IF(K29=0,"Sem horas",IF(L29&gt;N(F29),"Consome mais do que paga",IF(AND(N(G29)&gt;0,K29/G29&gt;1),"Estourou as horas",IF(AND(N(F29)&gt;0,(F29-L29)/F29&lt;0.2),"Margem baixa",IF(AND(N(G29)&gt;0,K29/G29&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="41" t="inlineStr">
@@ -6918,6 +7248,18 @@
           <t>Consultivo</t>
         </is>
       </c>
+      <c r="K30" s="39">
+        <f>IF(A30="","",N(H30)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A30))</f>
+        <v>26</v>
+      </c>
+      <c r="L30" s="39">
+        <f>IF(A30="","",N(H30)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A30))</f>
+        <v>1616.41774891775</v>
+      </c>
+      <c r="M30" s="39" t="str">
+        <f>IF(A30="","",IF(E30="Interno","Interno",IF(K30=0,"Sem horas",IF(L30&gt;N(F30),"Consome mais do que paga",IF(AND(N(G30)&gt;0,K30/G30&gt;1),"Estourou as horas",IF(AND(N(F30)&gt;0,(F30-L30)/F30&lt;0.2),"Margem baixa",IF(AND(N(G30)&gt;0,K30/G30&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="41" t="inlineStr">
@@ -6959,6 +7301,18 @@
           <t>Execução</t>
         </is>
       </c>
+      <c r="K31" s="39">
+        <f>IF(A31="","",N(H31)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A31))</f>
+        <v>58</v>
+      </c>
+      <c r="L31" s="39">
+        <f>IF(A31="","",N(H31)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A31))</f>
+        <v>3798.7012987013</v>
+      </c>
+      <c r="M31" s="39" t="str">
+        <f>IF(A31="","",IF(E31="Interno","Interno",IF(K31=0,"Sem horas",IF(L31&gt;N(F31),"Consome mais do que paga",IF(AND(N(G31)&gt;0,K31/G31&gt;1),"Estourou as horas",IF(AND(N(F31)&gt;0,(F31-L31)/F31&lt;0.2),"Margem baixa",IF(AND(N(G31)&gt;0,K31/G31&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="41" t="inlineStr">
@@ -7000,6 +7354,18 @@
           <t>Inicial</t>
         </is>
       </c>
+      <c r="K32" s="39">
+        <f>IF(A32="","",N(H32)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A32))</f>
+        <v>24</v>
+      </c>
+      <c r="L32" s="39">
+        <f>IF(A32="","",N(H32)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A32))</f>
+        <v>1587.94372294372</v>
+      </c>
+      <c r="M32" s="39" t="str">
+        <f>IF(A32="","",IF(E32="Interno","Interno",IF(K32=0,"Sem horas",IF(L32&gt;N(F32),"Consome mais do que paga",IF(AND(N(G32)&gt;0,K32/G32&gt;1),"Estourou as horas",IF(AND(N(F32)&gt;0,(F32-L32)/F32&lt;0.2),"Margem baixa",IF(AND(N(G32)&gt;0,K32/G32&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Saudável</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="41" t="inlineStr">
@@ -7041,6 +7407,18 @@
           <t>Sentença</t>
         </is>
       </c>
+      <c r="K33" s="39">
+        <f>IF(A33="","",N(H33)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A33))</f>
+        <v>40</v>
+      </c>
+      <c r="L33" s="39">
+        <f>IF(A33="","",N(H33)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A33))</f>
+        <v>2393.16017316017</v>
+      </c>
+      <c r="M33" s="39" t="str">
+        <f>IF(A33="","",IF(E33="Interno","Interno",IF(K33=0,"Sem horas",IF(L33&gt;N(F33),"Consome mais do que paga",IF(AND(N(G33)&gt;0,K33/G33&gt;1),"Estourou as horas",IF(AND(N(F33)&gt;0,(F33-L33)/F33&lt;0.2),"Margem baixa",IF(AND(N(G33)&gt;0,K33/G33&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="41" t="inlineStr">
@@ -7082,6 +7460,18 @@
           <t>Recurso</t>
         </is>
       </c>
+      <c r="K34" s="39">
+        <f>IF(A34="","",N(H34)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A34))</f>
+        <v>30</v>
+      </c>
+      <c r="L34" s="39">
+        <f>IF(A34="","",N(H34)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A34))</f>
+        <v>1921.94805194805</v>
+      </c>
+      <c r="M34" s="39" t="str">
+        <f>IF(A34="","",IF(E34="Interno","Interno",IF(K34=0,"Sem horas",IF(L34&gt;N(F34),"Consome mais do que paga",IF(AND(N(G34)&gt;0,K34/G34&gt;1),"Estourou as horas",IF(AND(N(F34)&gt;0,(F34-L34)/F34&lt;0.2),"Margem baixa",IF(AND(N(G34)&gt;0,K34/G34&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="41" t="inlineStr">
@@ -7123,6 +7513,18 @@
           <t>Encerrado</t>
         </is>
       </c>
+      <c r="K35" s="39">
+        <f>IF(A35="","",N(H35)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A35))</f>
+        <v>64</v>
+      </c>
+      <c r="L35" s="39">
+        <f>IF(A35="","",N(H35)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A35))</f>
+        <v>4228.57142857143</v>
+      </c>
+      <c r="M35" s="39" t="str">
+        <f>IF(A35="","",IF(E35="Interno","Interno",IF(K35=0,"Sem horas",IF(L35&gt;N(F35),"Consome mais do que paga",IF(AND(N(G35)&gt;0,K35/G35&gt;1),"Estourou as horas",IF(AND(N(F35)&gt;0,(F35-L35)/F35&lt;0.2),"Margem baixa",IF(AND(N(G35)&gt;0,K35/G35&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="41" t="inlineStr">
@@ -7164,6 +7566,18 @@
           <t>Encerrado</t>
         </is>
       </c>
+      <c r="K36" s="39">
+        <f>IF(A36="","",N(H36)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A36))</f>
+        <v>120</v>
+      </c>
+      <c r="L36" s="39">
+        <f>IF(A36="","",N(H36)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A36))</f>
+        <v>7928.57142857143</v>
+      </c>
+      <c r="M36" s="39" t="str">
+        <f>IF(A36="","",IF(E36="Interno","Interno",IF(K36=0,"Sem horas",IF(L36&gt;N(F36),"Consome mais do que paga",IF(AND(N(G36)&gt;0,K36/G36&gt;1),"Estourou as horas",IF(AND(N(F36)&gt;0,(F36-L36)/F36&lt;0.2),"Margem baixa",IF(AND(N(G36)&gt;0,K36/G36&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="41" t="inlineStr">
@@ -7205,6 +7619,18 @@
           <t>Encerrado</t>
         </is>
       </c>
+      <c r="K37" s="39">
+        <f>IF(A37="","",N(H37)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A37))</f>
+        <v>50</v>
+      </c>
+      <c r="L37" s="39">
+        <f>IF(A37="","",N(H37)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A37))</f>
+        <v>3303.57142857143</v>
+      </c>
+      <c r="M37" s="39" t="str">
+        <f>IF(A37="","",IF(E37="Interno","Interno",IF(K37=0,"Sem horas",IF(L37&gt;N(F37),"Consome mais do que paga",IF(AND(N(G37)&gt;0,K37/G37&gt;1),"Estourou as horas",IF(AND(N(F37)&gt;0,(F37-L37)/F37&lt;0.2),"Margem baixa",IF(AND(N(G37)&gt;0,K37/G37&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="41" t="inlineStr">
@@ -7246,6 +7672,18 @@
           <t>Encerrado</t>
         </is>
       </c>
+      <c r="K38" s="39">
+        <f>IF(A38="","",N(H38)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A38))</f>
+        <v>40</v>
+      </c>
+      <c r="L38" s="39">
+        <f>IF(A38="","",N(H38)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A38))</f>
+        <v>2642.85714285714</v>
+      </c>
+      <c r="M38" s="39" t="str">
+        <f>IF(A38="","",IF(E38="Interno","Interno",IF(K38=0,"Sem horas",IF(L38&gt;N(F38),"Consome mais do que paga",IF(AND(N(G38)&gt;0,K38/G38&gt;1),"Estourou as horas",IF(AND(N(F38)&gt;0,(F38-L38)/F38&lt;0.2),"Margem baixa",IF(AND(N(G38)&gt;0,K38/G38&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Perto do limite</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="41" t="inlineStr">
@@ -7287,6 +7725,18 @@
           <t>Encerrado</t>
         </is>
       </c>
+      <c r="K39" s="39">
+        <f>IF(A39="","",N(H39)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A39))</f>
+        <v>100</v>
+      </c>
+      <c r="L39" s="39">
+        <f>IF(A39="","",N(H39)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A39))</f>
+        <v>6553.63636363636</v>
+      </c>
+      <c r="M39" s="39" t="str">
+        <f>IF(A39="","",IF(E39="Interno","Interno",IF(K39=0,"Sem horas",IF(L39&gt;N(F39),"Consome mais do que paga",IF(AND(N(G39)&gt;0,K39/G39&gt;1),"Estourou as horas",IF(AND(N(F39)&gt;0,(F39-L39)/F39&lt;0.2),"Margem baixa",IF(AND(N(G39)&gt;0,K39/G39&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="41" t="inlineStr">
@@ -7328,6 +7778,18 @@
           <t>Encerrado</t>
         </is>
       </c>
+      <c r="K40" s="39">
+        <f>IF(A40="","",N(H40)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A40))</f>
+        <v>58</v>
+      </c>
+      <c r="L40" s="39">
+        <f>IF(A40="","",N(H40)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A40))</f>
+        <v>3882.30519480519</v>
+      </c>
+      <c r="M40" s="39" t="str">
+        <f>IF(A40="","",IF(E40="Interno","Interno",IF(K40=0,"Sem horas",IF(L40&gt;N(F40),"Consome mais do que paga",IF(AND(N(G40)&gt;0,K40/G40&gt;1),"Estourou as horas",IF(AND(N(F40)&gt;0,(F40-L40)/F40&lt;0.2),"Margem baixa",IF(AND(N(G40)&gt;0,K40/G40&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="41" t="inlineStr">
@@ -7369,6 +7831,18 @@
           <t>Encerrado</t>
         </is>
       </c>
+      <c r="K41" s="39">
+        <f>IF(A41="","",N(H41)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A41))</f>
+        <v>44</v>
+      </c>
+      <c r="L41" s="39">
+        <f>IF(A41="","",N(H41)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A41))</f>
+        <v>2907.14285714286</v>
+      </c>
+      <c r="M41" s="39" t="str">
+        <f>IF(A41="","",IF(E41="Interno","Interno",IF(K41=0,"Sem horas",IF(L41&gt;N(F41),"Consome mais do que paga",IF(AND(N(G41)&gt;0,K41/G41&gt;1),"Estourou as horas",IF(AND(N(F41)&gt;0,(F41-L41)/F41&lt;0.2),"Margem baixa",IF(AND(N(G41)&gt;0,K41/G41&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="41" t="inlineStr">
@@ -7410,6 +7884,18 @@
           <t>Encerrado</t>
         </is>
       </c>
+      <c r="K42" s="39">
+        <f>IF(A42="","",N(H42)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A42))</f>
+        <v>76</v>
+      </c>
+      <c r="L42" s="39">
+        <f>IF(A42="","",N(H42)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A42))</f>
+        <v>5021.42857142857</v>
+      </c>
+      <c r="M42" s="39" t="str">
+        <f>IF(A42="","",IF(E42="Interno","Interno",IF(K42=0,"Sem horas",IF(L42&gt;N(F42),"Consome mais do que paga",IF(AND(N(G42)&gt;0,K42/G42&gt;1),"Estourou as horas",IF(AND(N(F42)&gt;0,(F42-L42)/F42&lt;0.2),"Margem baixa",IF(AND(N(G42)&gt;0,K42/G42&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Estourou as horas</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="41" t="inlineStr">
@@ -7447,6 +7933,18 @@
         <v>0</v>
       </c>
       <c r="I43" s="42" t="n"/>
+      <c r="K43" s="39">
+        <f>IF(A43="","",N(H43)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A43))</f>
+        <v>51.5</v>
+      </c>
+      <c r="L43" s="39">
+        <f>IF(A43="","",N(H43)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A43))</f>
+        <v>3216.52056277056</v>
+      </c>
+      <c r="M43" s="39" t="str">
+        <f>IF(A43="","",IF(E43="Interno","Interno",IF(K43=0,"Sem horas",IF(L43&gt;N(F43),"Consome mais do que paga",IF(AND(N(G43)&gt;0,K43/G43&gt;1),"Estourou as horas",IF(AND(N(F43)&gt;0,(F43-L43)/F43&lt;0.2),"Margem baixa",IF(AND(N(G43)&gt;0,K43/G43&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Interno</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="41" t="inlineStr">
@@ -7484,6 +7982,18 @@
         <v>0</v>
       </c>
       <c r="I44" s="42" t="n"/>
+      <c r="K44" s="39">
+        <f>IF(A44="","",N(H44)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A44))</f>
+        <v>15</v>
+      </c>
+      <c r="L44" s="39">
+        <f>IF(A44="","",N(H44)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A44))</f>
+        <v>1091.3961038961</v>
+      </c>
+      <c r="M44" s="39" t="str">
+        <f>IF(A44="","",IF(E44="Interno","Interno",IF(K44=0,"Sem horas",IF(L44&gt;N(F44),"Consome mais do que paga",IF(AND(N(G44)&gt;0,K44/G44&gt;1),"Estourou as horas",IF(AND(N(F44)&gt;0,(F44-L44)/F44&lt;0.2),"Margem baixa",IF(AND(N(G44)&gt;0,K44/G44&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v>Interno</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="41" t="n"/>
@@ -7495,6 +8005,18 @@
       <c r="G45" s="46" t="n"/>
       <c r="H45" s="47" t="n"/>
       <c r="I45" s="42" t="n"/>
+      <c r="K45" s="39">
+        <f>IF(A45="","",N(H45)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A45))</f>
+        <v/>
+      </c>
+      <c r="L45" s="39">
+        <f>IF(A45="","",N(H45)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A45))</f>
+        <v/>
+      </c>
+      <c r="M45" s="39">
+        <f>IF(A45="","",IF(E45="Interno","Interno",IF(K45=0,"Sem horas",IF(L45&gt;N(F45),"Consome mais do que paga",IF(AND(N(G45)&gt;0,K45/G45&gt;1),"Estourou as horas",IF(AND(N(F45)&gt;0,(F45-L45)/F45&lt;0.2),"Margem baixa",IF(AND(N(G45)&gt;0,K45/G45&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="41" t="n"/>
@@ -7506,6 +8028,18 @@
       <c r="G46" s="46" t="n"/>
       <c r="H46" s="47" t="n"/>
       <c r="I46" s="42" t="n"/>
+      <c r="K46" s="39">
+        <f>IF(A46="","",N(H46)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A46))</f>
+        <v/>
+      </c>
+      <c r="L46" s="39">
+        <f>IF(A46="","",N(H46)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A46))</f>
+        <v/>
+      </c>
+      <c r="M46" s="39">
+        <f>IF(A46="","",IF(E46="Interno","Interno",IF(K46=0,"Sem horas",IF(L46&gt;N(F46),"Consome mais do que paga",IF(AND(N(G46)&gt;0,K46/G46&gt;1),"Estourou as horas",IF(AND(N(F46)&gt;0,(F46-L46)/F46&lt;0.2),"Margem baixa",IF(AND(N(G46)&gt;0,K46/G46&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="41" t="n"/>
@@ -7517,6 +8051,18 @@
       <c r="G47" s="46" t="n"/>
       <c r="H47" s="47" t="n"/>
       <c r="I47" s="42" t="n"/>
+      <c r="K47" s="39">
+        <f>IF(A47="","",N(H47)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A47))</f>
+        <v/>
+      </c>
+      <c r="L47" s="39">
+        <f>IF(A47="","",N(H47)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A47))</f>
+        <v/>
+      </c>
+      <c r="M47" s="39">
+        <f>IF(A47="","",IF(E47="Interno","Interno",IF(K47=0,"Sem horas",IF(L47&gt;N(F47),"Consome mais do que paga",IF(AND(N(G47)&gt;0,K47/G47&gt;1),"Estourou as horas",IF(AND(N(F47)&gt;0,(F47-L47)/F47&lt;0.2),"Margem baixa",IF(AND(N(G47)&gt;0,K47/G47&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="41" t="n"/>
@@ -7528,6 +8074,18 @@
       <c r="G48" s="46" t="n"/>
       <c r="H48" s="47" t="n"/>
       <c r="I48" s="42" t="n"/>
+      <c r="K48" s="39">
+        <f>IF(A48="","",N(H48)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A48))</f>
+        <v/>
+      </c>
+      <c r="L48" s="39">
+        <f>IF(A48="","",N(H48)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A48))</f>
+        <v/>
+      </c>
+      <c r="M48" s="39">
+        <f>IF(A48="","",IF(E48="Interno","Interno",IF(K48=0,"Sem horas",IF(L48&gt;N(F48),"Consome mais do que paga",IF(AND(N(G48)&gt;0,K48/G48&gt;1),"Estourou as horas",IF(AND(N(F48)&gt;0,(F48-L48)/F48&lt;0.2),"Margem baixa",IF(AND(N(G48)&gt;0,K48/G48&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="41" t="n"/>
@@ -7539,6 +8097,18 @@
       <c r="G49" s="46" t="n"/>
       <c r="H49" s="47" t="n"/>
       <c r="I49" s="42" t="n"/>
+      <c r="K49" s="39">
+        <f>IF(A49="","",N(H49)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A49))</f>
+        <v/>
+      </c>
+      <c r="L49" s="39">
+        <f>IF(A49="","",N(H49)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A49))</f>
+        <v/>
+      </c>
+      <c r="M49" s="39">
+        <f>IF(A49="","",IF(E49="Interno","Interno",IF(K49=0,"Sem horas",IF(L49&gt;N(F49),"Consome mais do que paga",IF(AND(N(G49)&gt;0,K49/G49&gt;1),"Estourou as horas",IF(AND(N(F49)&gt;0,(F49-L49)/F49&lt;0.2),"Margem baixa",IF(AND(N(G49)&gt;0,K49/G49&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="41" t="n"/>
@@ -7550,6 +8120,18 @@
       <c r="G50" s="46" t="n"/>
       <c r="H50" s="47" t="n"/>
       <c r="I50" s="42" t="n"/>
+      <c r="K50" s="39">
+        <f>IF(A50="","",N(H50)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A50))</f>
+        <v/>
+      </c>
+      <c r="L50" s="39">
+        <f>IF(A50="","",N(H50)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A50))</f>
+        <v/>
+      </c>
+      <c r="M50" s="39">
+        <f>IF(A50="","",IF(E50="Interno","Interno",IF(K50=0,"Sem horas",IF(L50&gt;N(F50),"Consome mais do que paga",IF(AND(N(G50)&gt;0,K50/G50&gt;1),"Estourou as horas",IF(AND(N(F50)&gt;0,(F50-L50)/F50&lt;0.2),"Margem baixa",IF(AND(N(G50)&gt;0,K50/G50&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="41" t="n"/>
@@ -7561,6 +8143,18 @@
       <c r="G51" s="46" t="n"/>
       <c r="H51" s="47" t="n"/>
       <c r="I51" s="42" t="n"/>
+      <c r="K51" s="39">
+        <f>IF(A51="","",N(H51)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A51))</f>
+        <v/>
+      </c>
+      <c r="L51" s="39">
+        <f>IF(A51="","",N(H51)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A51))</f>
+        <v/>
+      </c>
+      <c r="M51" s="39">
+        <f>IF(A51="","",IF(E51="Interno","Interno",IF(K51=0,"Sem horas",IF(L51&gt;N(F51),"Consome mais do que paga",IF(AND(N(G51)&gt;0,K51/G51&gt;1),"Estourou as horas",IF(AND(N(F51)&gt;0,(F51-L51)/F51&lt;0.2),"Margem baixa",IF(AND(N(G51)&gt;0,K51/G51&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="41" t="n"/>
@@ -7572,6 +8166,18 @@
       <c r="G52" s="46" t="n"/>
       <c r="H52" s="47" t="n"/>
       <c r="I52" s="42" t="n"/>
+      <c r="K52" s="39">
+        <f>IF(A52="","",N(H52)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A52))</f>
+        <v/>
+      </c>
+      <c r="L52" s="39">
+        <f>IF(A52="","",N(H52)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A52))</f>
+        <v/>
+      </c>
+      <c r="M52" s="39">
+        <f>IF(A52="","",IF(E52="Interno","Interno",IF(K52=0,"Sem horas",IF(L52&gt;N(F52),"Consome mais do que paga",IF(AND(N(G52)&gt;0,K52/G52&gt;1),"Estourou as horas",IF(AND(N(F52)&gt;0,(F52-L52)/F52&lt;0.2),"Margem baixa",IF(AND(N(G52)&gt;0,K52/G52&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="41" t="n"/>
@@ -7583,6 +8189,18 @@
       <c r="G53" s="46" t="n"/>
       <c r="H53" s="47" t="n"/>
       <c r="I53" s="42" t="n"/>
+      <c r="K53" s="39">
+        <f>IF(A53="","",N(H53)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A53))</f>
+        <v/>
+      </c>
+      <c r="L53" s="39">
+        <f>IF(A53="","",N(H53)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A53))</f>
+        <v/>
+      </c>
+      <c r="M53" s="39">
+        <f>IF(A53="","",IF(E53="Interno","Interno",IF(K53=0,"Sem horas",IF(L53&gt;N(F53),"Consome mais do que paga",IF(AND(N(G53)&gt;0,K53/G53&gt;1),"Estourou as horas",IF(AND(N(F53)&gt;0,(F53-L53)/F53&lt;0.2),"Margem baixa",IF(AND(N(G53)&gt;0,K53/G53&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="41" t="n"/>
@@ -7594,6 +8212,18 @@
       <c r="G54" s="46" t="n"/>
       <c r="H54" s="47" t="n"/>
       <c r="I54" s="42" t="n"/>
+      <c r="K54" s="39">
+        <f>IF(A54="","",N(H54)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A54))</f>
+        <v/>
+      </c>
+      <c r="L54" s="39">
+        <f>IF(A54="","",N(H54)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A54))</f>
+        <v/>
+      </c>
+      <c r="M54" s="39">
+        <f>IF(A54="","",IF(E54="Interno","Interno",IF(K54=0,"Sem horas",IF(L54&gt;N(F54),"Consome mais do que paga",IF(AND(N(G54)&gt;0,K54/G54&gt;1),"Estourou as horas",IF(AND(N(F54)&gt;0,(F54-L54)/F54&lt;0.2),"Margem baixa",IF(AND(N(G54)&gt;0,K54/G54&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="41" t="n"/>
@@ -7605,6 +8235,18 @@
       <c r="G55" s="46" t="n"/>
       <c r="H55" s="47" t="n"/>
       <c r="I55" s="42" t="n"/>
+      <c r="K55" s="39">
+        <f>IF(A55="","",N(H55)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A55))</f>
+        <v/>
+      </c>
+      <c r="L55" s="39">
+        <f>IF(A55="","",N(H55)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A55))</f>
+        <v/>
+      </c>
+      <c r="M55" s="39">
+        <f>IF(A55="","",IF(E55="Interno","Interno",IF(K55=0,"Sem horas",IF(L55&gt;N(F55),"Consome mais do que paga",IF(AND(N(G55)&gt;0,K55/G55&gt;1),"Estourou as horas",IF(AND(N(F55)&gt;0,(F55-L55)/F55&lt;0.2),"Margem baixa",IF(AND(N(G55)&gt;0,K55/G55&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="41" t="n"/>
@@ -7616,6 +8258,18 @@
       <c r="G56" s="46" t="n"/>
       <c r="H56" s="47" t="n"/>
       <c r="I56" s="42" t="n"/>
+      <c r="K56" s="39">
+        <f>IF(A56="","",N(H56)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A56))</f>
+        <v/>
+      </c>
+      <c r="L56" s="39">
+        <f>IF(A56="","",N(H56)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A56))</f>
+        <v/>
+      </c>
+      <c r="M56" s="39">
+        <f>IF(A56="","",IF(E56="Interno","Interno",IF(K56=0,"Sem horas",IF(L56&gt;N(F56),"Consome mais do que paga",IF(AND(N(G56)&gt;0,K56/G56&gt;1),"Estourou as horas",IF(AND(N(F56)&gt;0,(F56-L56)/F56&lt;0.2),"Margem baixa",IF(AND(N(G56)&gt;0,K56/G56&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="41" t="n"/>
@@ -7627,6 +8281,18 @@
       <c r="G57" s="46" t="n"/>
       <c r="H57" s="47" t="n"/>
       <c r="I57" s="42" t="n"/>
+      <c r="K57" s="39">
+        <f>IF(A57="","",N(H57)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A57))</f>
+        <v/>
+      </c>
+      <c r="L57" s="39">
+        <f>IF(A57="","",N(H57)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A57))</f>
+        <v/>
+      </c>
+      <c r="M57" s="39">
+        <f>IF(A57="","",IF(E57="Interno","Interno",IF(K57=0,"Sem horas",IF(L57&gt;N(F57),"Consome mais do que paga",IF(AND(N(G57)&gt;0,K57/G57&gt;1),"Estourou as horas",IF(AND(N(F57)&gt;0,(F57-L57)/F57&lt;0.2),"Margem baixa",IF(AND(N(G57)&gt;0,K57/G57&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="41" t="n"/>
@@ -7638,6 +8304,18 @@
       <c r="G58" s="46" t="n"/>
       <c r="H58" s="47" t="n"/>
       <c r="I58" s="42" t="n"/>
+      <c r="K58" s="39">
+        <f>IF(A58="","",N(H58)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A58))</f>
+        <v/>
+      </c>
+      <c r="L58" s="39">
+        <f>IF(A58="","",N(H58)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A58))</f>
+        <v/>
+      </c>
+      <c r="M58" s="39">
+        <f>IF(A58="","",IF(E58="Interno","Interno",IF(K58=0,"Sem horas",IF(L58&gt;N(F58),"Consome mais do que paga",IF(AND(N(G58)&gt;0,K58/G58&gt;1),"Estourou as horas",IF(AND(N(F58)&gt;0,(F58-L58)/F58&lt;0.2),"Margem baixa",IF(AND(N(G58)&gt;0,K58/G58&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="41" t="n"/>
@@ -7649,6 +8327,18 @@
       <c r="G59" s="46" t="n"/>
       <c r="H59" s="47" t="n"/>
       <c r="I59" s="42" t="n"/>
+      <c r="K59" s="39">
+        <f>IF(A59="","",N(H59)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A59))</f>
+        <v/>
+      </c>
+      <c r="L59" s="39">
+        <f>IF(A59="","",N(H59)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A59))</f>
+        <v/>
+      </c>
+      <c r="M59" s="39">
+        <f>IF(A59="","",IF(E59="Interno","Interno",IF(K59=0,"Sem horas",IF(L59&gt;N(F59),"Consome mais do que paga",IF(AND(N(G59)&gt;0,K59/G59&gt;1),"Estourou as horas",IF(AND(N(F59)&gt;0,(F59-L59)/F59&lt;0.2),"Margem baixa",IF(AND(N(G59)&gt;0,K59/G59&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="41" t="n"/>
@@ -7660,6 +8350,18 @@
       <c r="G60" s="46" t="n"/>
       <c r="H60" s="47" t="n"/>
       <c r="I60" s="42" t="n"/>
+      <c r="K60" s="39">
+        <f>IF(A60="","",N(H60)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A60))</f>
+        <v/>
+      </c>
+      <c r="L60" s="39">
+        <f>IF(A60="","",N(H60)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A60))</f>
+        <v/>
+      </c>
+      <c r="M60" s="39">
+        <f>IF(A60="","",IF(E60="Interno","Interno",IF(K60=0,"Sem horas",IF(L60&gt;N(F60),"Consome mais do que paga",IF(AND(N(G60)&gt;0,K60/G60&gt;1),"Estourou as horas",IF(AND(N(F60)&gt;0,(F60-L60)/F60&lt;0.2),"Margem baixa",IF(AND(N(G60)&gt;0,K60/G60&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="41" t="n"/>
@@ -7671,6 +8373,18 @@
       <c r="G61" s="46" t="n"/>
       <c r="H61" s="47" t="n"/>
       <c r="I61" s="42" t="n"/>
+      <c r="K61" s="39">
+        <f>IF(A61="","",N(H61)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A61))</f>
+        <v/>
+      </c>
+      <c r="L61" s="39">
+        <f>IF(A61="","",N(H61)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A61))</f>
+        <v/>
+      </c>
+      <c r="M61" s="39">
+        <f>IF(A61="","",IF(E61="Interno","Interno",IF(K61=0,"Sem horas",IF(L61&gt;N(F61),"Consome mais do que paga",IF(AND(N(G61)&gt;0,K61/G61&gt;1),"Estourou as horas",IF(AND(N(F61)&gt;0,(F61-L61)/F61&lt;0.2),"Margem baixa",IF(AND(N(G61)&gt;0,K61/G61&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="41" t="n"/>
@@ -7682,6 +8396,18 @@
       <c r="G62" s="46" t="n"/>
       <c r="H62" s="47" t="n"/>
       <c r="I62" s="42" t="n"/>
+      <c r="K62" s="39">
+        <f>IF(A62="","",N(H62)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A62))</f>
+        <v/>
+      </c>
+      <c r="L62" s="39">
+        <f>IF(A62="","",N(H62)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A62))</f>
+        <v/>
+      </c>
+      <c r="M62" s="39">
+        <f>IF(A62="","",IF(E62="Interno","Interno",IF(K62=0,"Sem horas",IF(L62&gt;N(F62),"Consome mais do que paga",IF(AND(N(G62)&gt;0,K62/G62&gt;1),"Estourou as horas",IF(AND(N(F62)&gt;0,(F62-L62)/F62&lt;0.2),"Margem baixa",IF(AND(N(G62)&gt;0,K62/G62&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="41" t="n"/>
@@ -7693,6 +8419,18 @@
       <c r="G63" s="46" t="n"/>
       <c r="H63" s="47" t="n"/>
       <c r="I63" s="42" t="n"/>
+      <c r="K63" s="39">
+        <f>IF(A63="","",N(H63)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A63))</f>
+        <v/>
+      </c>
+      <c r="L63" s="39">
+        <f>IF(A63="","",N(H63)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A63))</f>
+        <v/>
+      </c>
+      <c r="M63" s="39">
+        <f>IF(A63="","",IF(E63="Interno","Interno",IF(K63=0,"Sem horas",IF(L63&gt;N(F63),"Consome mais do que paga",IF(AND(N(G63)&gt;0,K63/G63&gt;1),"Estourou as horas",IF(AND(N(F63)&gt;0,(F63-L63)/F63&lt;0.2),"Margem baixa",IF(AND(N(G63)&gt;0,K63/G63&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="41" t="n"/>
@@ -7704,6 +8442,18 @@
       <c r="G64" s="46" t="n"/>
       <c r="H64" s="47" t="n"/>
       <c r="I64" s="42" t="n"/>
+      <c r="K64" s="39">
+        <f>IF(A64="","",N(H64)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A64))</f>
+        <v/>
+      </c>
+      <c r="L64" s="39">
+        <f>IF(A64="","",N(H64)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A64))</f>
+        <v/>
+      </c>
+      <c r="M64" s="39">
+        <f>IF(A64="","",IF(E64="Interno","Interno",IF(K64=0,"Sem horas",IF(L64&gt;N(F64),"Consome mais do que paga",IF(AND(N(G64)&gt;0,K64/G64&gt;1),"Estourou as horas",IF(AND(N(F64)&gt;0,(F64-L64)/F64&lt;0.2),"Margem baixa",IF(AND(N(G64)&gt;0,K64/G64&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="41" t="n"/>
@@ -7715,6 +8465,18 @@
       <c r="G65" s="46" t="n"/>
       <c r="H65" s="47" t="n"/>
       <c r="I65" s="42" t="n"/>
+      <c r="K65" s="39">
+        <f>IF(A65="","",N(H65)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A65))</f>
+        <v/>
+      </c>
+      <c r="L65" s="39">
+        <f>IF(A65="","",N(H65)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A65))</f>
+        <v/>
+      </c>
+      <c r="M65" s="39">
+        <f>IF(A65="","",IF(E65="Interno","Interno",IF(K65=0,"Sem horas",IF(L65&gt;N(F65),"Consome mais do que paga",IF(AND(N(G65)&gt;0,K65/G65&gt;1),"Estourou as horas",IF(AND(N(F65)&gt;0,(F65-L65)/F65&lt;0.2),"Margem baixa",IF(AND(N(G65)&gt;0,K65/G65&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="41" t="n"/>
@@ -7726,6 +8488,18 @@
       <c r="G66" s="46" t="n"/>
       <c r="H66" s="47" t="n"/>
       <c r="I66" s="42" t="n"/>
+      <c r="K66" s="39">
+        <f>IF(A66="","",N(H66)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A66))</f>
+        <v/>
+      </c>
+      <c r="L66" s="39">
+        <f>IF(A66="","",N(H66)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A66))</f>
+        <v/>
+      </c>
+      <c r="M66" s="39">
+        <f>IF(A66="","",IF(E66="Interno","Interno",IF(K66=0,"Sem horas",IF(L66&gt;N(F66),"Consome mais do que paga",IF(AND(N(G66)&gt;0,K66/G66&gt;1),"Estourou as horas",IF(AND(N(F66)&gt;0,(F66-L66)/F66&lt;0.2),"Margem baixa",IF(AND(N(G66)&gt;0,K66/G66&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="41" t="n"/>
@@ -7737,6 +8511,18 @@
       <c r="G67" s="46" t="n"/>
       <c r="H67" s="47" t="n"/>
       <c r="I67" s="42" t="n"/>
+      <c r="K67" s="39">
+        <f>IF(A67="","",N(H67)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A67))</f>
+        <v/>
+      </c>
+      <c r="L67" s="39">
+        <f>IF(A67="","",N(H67)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A67))</f>
+        <v/>
+      </c>
+      <c r="M67" s="39">
+        <f>IF(A67="","",IF(E67="Interno","Interno",IF(K67=0,"Sem horas",IF(L67&gt;N(F67),"Consome mais do que paga",IF(AND(N(G67)&gt;0,K67/G67&gt;1),"Estourou as horas",IF(AND(N(F67)&gt;0,(F67-L67)/F67&lt;0.2),"Margem baixa",IF(AND(N(G67)&gt;0,K67/G67&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="41" t="n"/>
@@ -7748,6 +8534,18 @@
       <c r="G68" s="46" t="n"/>
       <c r="H68" s="47" t="n"/>
       <c r="I68" s="42" t="n"/>
+      <c r="K68" s="39">
+        <f>IF(A68="","",N(H68)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A68))</f>
+        <v/>
+      </c>
+      <c r="L68" s="39">
+        <f>IF(A68="","",N(H68)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A68))</f>
+        <v/>
+      </c>
+      <c r="M68" s="39">
+        <f>IF(A68="","",IF(E68="Interno","Interno",IF(K68=0,"Sem horas",IF(L68&gt;N(F68),"Consome mais do que paga",IF(AND(N(G68)&gt;0,K68/G68&gt;1),"Estourou as horas",IF(AND(N(F68)&gt;0,(F68-L68)/F68&lt;0.2),"Margem baixa",IF(AND(N(G68)&gt;0,K68/G68&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="41" t="n"/>
@@ -7759,6 +8557,18 @@
       <c r="G69" s="46" t="n"/>
       <c r="H69" s="47" t="n"/>
       <c r="I69" s="42" t="n"/>
+      <c r="K69" s="39">
+        <f>IF(A69="","",N(H69)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A69))</f>
+        <v/>
+      </c>
+      <c r="L69" s="39">
+        <f>IF(A69="","",N(H69)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A69))</f>
+        <v/>
+      </c>
+      <c r="M69" s="39">
+        <f>IF(A69="","",IF(E69="Interno","Interno",IF(K69=0,"Sem horas",IF(L69&gt;N(F69),"Consome mais do que paga",IF(AND(N(G69)&gt;0,K69/G69&gt;1),"Estourou as horas",IF(AND(N(F69)&gt;0,(F69-L69)/F69&lt;0.2),"Margem baixa",IF(AND(N(G69)&gt;0,K69/G69&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="41" t="n"/>
@@ -7770,6 +8580,18 @@
       <c r="G70" s="46" t="n"/>
       <c r="H70" s="47" t="n"/>
       <c r="I70" s="42" t="n"/>
+      <c r="K70" s="39">
+        <f>IF(A70="","",N(H70)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A70))</f>
+        <v/>
+      </c>
+      <c r="L70" s="39">
+        <f>IF(A70="","",N(H70)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A70))</f>
+        <v/>
+      </c>
+      <c r="M70" s="39">
+        <f>IF(A70="","",IF(E70="Interno","Interno",IF(K70=0,"Sem horas",IF(L70&gt;N(F70),"Consome mais do que paga",IF(AND(N(G70)&gt;0,K70/G70&gt;1),"Estourou as horas",IF(AND(N(F70)&gt;0,(F70-L70)/F70&lt;0.2),"Margem baixa",IF(AND(N(G70)&gt;0,K70/G70&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="41" t="n"/>
@@ -7781,6 +8603,18 @@
       <c r="G71" s="46" t="n"/>
       <c r="H71" s="47" t="n"/>
       <c r="I71" s="42" t="n"/>
+      <c r="K71" s="39">
+        <f>IF(A71="","",N(H71)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A71))</f>
+        <v/>
+      </c>
+      <c r="L71" s="39">
+        <f>IF(A71="","",N(H71)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A71))</f>
+        <v/>
+      </c>
+      <c r="M71" s="39">
+        <f>IF(A71="","",IF(E71="Interno","Interno",IF(K71=0,"Sem horas",IF(L71&gt;N(F71),"Consome mais do que paga",IF(AND(N(G71)&gt;0,K71/G71&gt;1),"Estourou as horas",IF(AND(N(F71)&gt;0,(F71-L71)/F71&lt;0.2),"Margem baixa",IF(AND(N(G71)&gt;0,K71/G71&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="41" t="n"/>
@@ -7792,6 +8626,18 @@
       <c r="G72" s="46" t="n"/>
       <c r="H72" s="47" t="n"/>
       <c r="I72" s="42" t="n"/>
+      <c r="K72" s="39">
+        <f>IF(A72="","",N(H72)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A72))</f>
+        <v/>
+      </c>
+      <c r="L72" s="39">
+        <f>IF(A72="","",N(H72)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A72))</f>
+        <v/>
+      </c>
+      <c r="M72" s="39">
+        <f>IF(A72="","",IF(E72="Interno","Interno",IF(K72=0,"Sem horas",IF(L72&gt;N(F72),"Consome mais do que paga",IF(AND(N(G72)&gt;0,K72/G72&gt;1),"Estourou as horas",IF(AND(N(F72)&gt;0,(F72-L72)/F72&lt;0.2),"Margem baixa",IF(AND(N(G72)&gt;0,K72/G72&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="41" t="n"/>
@@ -7803,6 +8649,18 @@
       <c r="G73" s="46" t="n"/>
       <c r="H73" s="47" t="n"/>
       <c r="I73" s="42" t="n"/>
+      <c r="K73" s="39">
+        <f>IF(A73="","",N(H73)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A73))</f>
+        <v/>
+      </c>
+      <c r="L73" s="39">
+        <f>IF(A73="","",N(H73)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A73))</f>
+        <v/>
+      </c>
+      <c r="M73" s="39">
+        <f>IF(A73="","",IF(E73="Interno","Interno",IF(K73=0,"Sem horas",IF(L73&gt;N(F73),"Consome mais do que paga",IF(AND(N(G73)&gt;0,K73/G73&gt;1),"Estourou as horas",IF(AND(N(F73)&gt;0,(F73-L73)/F73&lt;0.2),"Margem baixa",IF(AND(N(G73)&gt;0,K73/G73&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="41" t="n"/>
@@ -7814,6 +8672,18 @@
       <c r="G74" s="46" t="n"/>
       <c r="H74" s="47" t="n"/>
       <c r="I74" s="42" t="n"/>
+      <c r="K74" s="39">
+        <f>IF(A74="","",N(H74)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A74))</f>
+        <v/>
+      </c>
+      <c r="L74" s="39">
+        <f>IF(A74="","",N(H74)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A74))</f>
+        <v/>
+      </c>
+      <c r="M74" s="39">
+        <f>IF(A74="","",IF(E74="Interno","Interno",IF(K74=0,"Sem horas",IF(L74&gt;N(F74),"Consome mais do que paga",IF(AND(N(G74)&gt;0,K74/G74&gt;1),"Estourou as horas",IF(AND(N(F74)&gt;0,(F74-L74)/F74&lt;0.2),"Margem baixa",IF(AND(N(G74)&gt;0,K74/G74&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="41" t="n"/>
@@ -7825,6 +8695,18 @@
       <c r="G75" s="46" t="n"/>
       <c r="H75" s="47" t="n"/>
       <c r="I75" s="42" t="n"/>
+      <c r="K75" s="39">
+        <f>IF(A75="","",N(H75)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A75))</f>
+        <v/>
+      </c>
+      <c r="L75" s="39">
+        <f>IF(A75="","",N(H75)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A75))</f>
+        <v/>
+      </c>
+      <c r="M75" s="39">
+        <f>IF(A75="","",IF(E75="Interno","Interno",IF(K75=0,"Sem horas",IF(L75&gt;N(F75),"Consome mais do que paga",IF(AND(N(G75)&gt;0,K75/G75&gt;1),"Estourou as horas",IF(AND(N(F75)&gt;0,(F75-L75)/F75&lt;0.2),"Margem baixa",IF(AND(N(G75)&gt;0,K75/G75&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="41" t="n"/>
@@ -7836,6 +8718,18 @@
       <c r="G76" s="46" t="n"/>
       <c r="H76" s="47" t="n"/>
       <c r="I76" s="42" t="n"/>
+      <c r="K76" s="39">
+        <f>IF(A76="","",N(H76)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A76))</f>
+        <v/>
+      </c>
+      <c r="L76" s="39">
+        <f>IF(A76="","",N(H76)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A76))</f>
+        <v/>
+      </c>
+      <c r="M76" s="39">
+        <f>IF(A76="","",IF(E76="Interno","Interno",IF(K76=0,"Sem horas",IF(L76&gt;N(F76),"Consome mais do que paga",IF(AND(N(G76)&gt;0,K76/G76&gt;1),"Estourou as horas",IF(AND(N(F76)&gt;0,(F76-L76)/F76&lt;0.2),"Margem baixa",IF(AND(N(G76)&gt;0,K76/G76&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="41" t="n"/>
@@ -7847,6 +8741,18 @@
       <c r="G77" s="46" t="n"/>
       <c r="H77" s="47" t="n"/>
       <c r="I77" s="42" t="n"/>
+      <c r="K77" s="39">
+        <f>IF(A77="","",N(H77)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A77))</f>
+        <v/>
+      </c>
+      <c r="L77" s="39">
+        <f>IF(A77="","",N(H77)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A77))</f>
+        <v/>
+      </c>
+      <c r="M77" s="39">
+        <f>IF(A77="","",IF(E77="Interno","Interno",IF(K77=0,"Sem horas",IF(L77&gt;N(F77),"Consome mais do que paga",IF(AND(N(G77)&gt;0,K77/G77&gt;1),"Estourou as horas",IF(AND(N(F77)&gt;0,(F77-L77)/F77&lt;0.2),"Margem baixa",IF(AND(N(G77)&gt;0,K77/G77&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="41" t="n"/>
@@ -7858,6 +8764,18 @@
       <c r="G78" s="46" t="n"/>
       <c r="H78" s="47" t="n"/>
       <c r="I78" s="42" t="n"/>
+      <c r="K78" s="39">
+        <f>IF(A78="","",N(H78)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A78))</f>
+        <v/>
+      </c>
+      <c r="L78" s="39">
+        <f>IF(A78="","",N(H78)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A78))</f>
+        <v/>
+      </c>
+      <c r="M78" s="39">
+        <f>IF(A78="","",IF(E78="Interno","Interno",IF(K78=0,"Sem horas",IF(L78&gt;N(F78),"Consome mais do que paga",IF(AND(N(G78)&gt;0,K78/G78&gt;1),"Estourou as horas",IF(AND(N(F78)&gt;0,(F78-L78)/F78&lt;0.2),"Margem baixa",IF(AND(N(G78)&gt;0,K78/G78&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="41" t="n"/>
@@ -7869,6 +8787,18 @@
       <c r="G79" s="46" t="n"/>
       <c r="H79" s="47" t="n"/>
       <c r="I79" s="42" t="n"/>
+      <c r="K79" s="39">
+        <f>IF(A79="","",N(H79)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A79))</f>
+        <v/>
+      </c>
+      <c r="L79" s="39">
+        <f>IF(A79="","",N(H79)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A79))</f>
+        <v/>
+      </c>
+      <c r="M79" s="39">
+        <f>IF(A79="","",IF(E79="Interno","Interno",IF(K79=0,"Sem horas",IF(L79&gt;N(F79),"Consome mais do que paga",IF(AND(N(G79)&gt;0,K79/G79&gt;1),"Estourou as horas",IF(AND(N(F79)&gt;0,(F79-L79)/F79&lt;0.2),"Margem baixa",IF(AND(N(G79)&gt;0,K79/G79&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="41" t="n"/>
@@ -7880,6 +8810,18 @@
       <c r="G80" s="46" t="n"/>
       <c r="H80" s="47" t="n"/>
       <c r="I80" s="42" t="n"/>
+      <c r="K80" s="39">
+        <f>IF(A80="","",N(H80)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A80))</f>
+        <v/>
+      </c>
+      <c r="L80" s="39">
+        <f>IF(A80="","",N(H80)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A80))</f>
+        <v/>
+      </c>
+      <c r="M80" s="39">
+        <f>IF(A80="","",IF(E80="Interno","Interno",IF(K80=0,"Sem horas",IF(L80&gt;N(F80),"Consome mais do que paga",IF(AND(N(G80)&gt;0,K80/G80&gt;1),"Estourou as horas",IF(AND(N(F80)&gt;0,(F80-L80)/F80&lt;0.2),"Margem baixa",IF(AND(N(G80)&gt;0,K80/G80&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="41" t="n"/>
@@ -7891,6 +8833,18 @@
       <c r="G81" s="46" t="n"/>
       <c r="H81" s="47" t="n"/>
       <c r="I81" s="42" t="n"/>
+      <c r="K81" s="39">
+        <f>IF(A81="","",N(H81)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A81))</f>
+        <v/>
+      </c>
+      <c r="L81" s="39">
+        <f>IF(A81="","",N(H81)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A81))</f>
+        <v/>
+      </c>
+      <c r="M81" s="39">
+        <f>IF(A81="","",IF(E81="Interno","Interno",IF(K81=0,"Sem horas",IF(L81&gt;N(F81),"Consome mais do que paga",IF(AND(N(G81)&gt;0,K81/G81&gt;1),"Estourou as horas",IF(AND(N(F81)&gt;0,(F81-L81)/F81&lt;0.2),"Margem baixa",IF(AND(N(G81)&gt;0,K81/G81&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="41" t="n"/>
@@ -7902,6 +8856,18 @@
       <c r="G82" s="46" t="n"/>
       <c r="H82" s="47" t="n"/>
       <c r="I82" s="42" t="n"/>
+      <c r="K82" s="39">
+        <f>IF(A82="","",N(H82)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A82))</f>
+        <v/>
+      </c>
+      <c r="L82" s="39">
+        <f>IF(A82="","",N(H82)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A82))</f>
+        <v/>
+      </c>
+      <c r="M82" s="39">
+        <f>IF(A82="","",IF(E82="Interno","Interno",IF(K82=0,"Sem horas",IF(L82&gt;N(F82),"Consome mais do que paga",IF(AND(N(G82)&gt;0,K82/G82&gt;1),"Estourou as horas",IF(AND(N(F82)&gt;0,(F82-L82)/F82&lt;0.2),"Margem baixa",IF(AND(N(G82)&gt;0,K82/G82&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="41" t="n"/>
@@ -7913,6 +8879,18 @@
       <c r="G83" s="46" t="n"/>
       <c r="H83" s="47" t="n"/>
       <c r="I83" s="42" t="n"/>
+      <c r="K83" s="39">
+        <f>IF(A83="","",N(H83)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A83))</f>
+        <v/>
+      </c>
+      <c r="L83" s="39">
+        <f>IF(A83="","",N(H83)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A83))</f>
+        <v/>
+      </c>
+      <c r="M83" s="39">
+        <f>IF(A83="","",IF(E83="Interno","Interno",IF(K83=0,"Sem horas",IF(L83&gt;N(F83),"Consome mais do que paga",IF(AND(N(G83)&gt;0,K83/G83&gt;1),"Estourou as horas",IF(AND(N(F83)&gt;0,(F83-L83)/F83&lt;0.2),"Margem baixa",IF(AND(N(G83)&gt;0,K83/G83&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="41" t="n"/>
@@ -7924,6 +8902,18 @@
       <c r="G84" s="46" t="n"/>
       <c r="H84" s="47" t="n"/>
       <c r="I84" s="42" t="n"/>
+      <c r="K84" s="39">
+        <f>IF(A84="","",N(H84)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A84))</f>
+        <v/>
+      </c>
+      <c r="L84" s="39">
+        <f>IF(A84="","",N(H84)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A84))</f>
+        <v/>
+      </c>
+      <c r="M84" s="39">
+        <f>IF(A84="","",IF(E84="Interno","Interno",IF(K84=0,"Sem horas",IF(L84&gt;N(F84),"Consome mais do que paga",IF(AND(N(G84)&gt;0,K84/G84&gt;1),"Estourou as horas",IF(AND(N(F84)&gt;0,(F84-L84)/F84&lt;0.2),"Margem baixa",IF(AND(N(G84)&gt;0,K84/G84&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="41" t="n"/>
@@ -7935,6 +8925,18 @@
       <c r="G85" s="46" t="n"/>
       <c r="H85" s="47" t="n"/>
       <c r="I85" s="42" t="n"/>
+      <c r="K85" s="39">
+        <f>IF(A85="","",N(H85)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A85))</f>
+        <v/>
+      </c>
+      <c r="L85" s="39">
+        <f>IF(A85="","",N(H85)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A85))</f>
+        <v/>
+      </c>
+      <c r="M85" s="39">
+        <f>IF(A85="","",IF(E85="Interno","Interno",IF(K85=0,"Sem horas",IF(L85&gt;N(F85),"Consome mais do que paga",IF(AND(N(G85)&gt;0,K85/G85&gt;1),"Estourou as horas",IF(AND(N(F85)&gt;0,(F85-L85)/F85&lt;0.2),"Margem baixa",IF(AND(N(G85)&gt;0,K85/G85&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="41" t="n"/>
@@ -7946,6 +8948,18 @@
       <c r="G86" s="46" t="n"/>
       <c r="H86" s="47" t="n"/>
       <c r="I86" s="42" t="n"/>
+      <c r="K86" s="39">
+        <f>IF(A86="","",N(H86)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A86))</f>
+        <v/>
+      </c>
+      <c r="L86" s="39">
+        <f>IF(A86="","",N(H86)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A86))</f>
+        <v/>
+      </c>
+      <c r="M86" s="39">
+        <f>IF(A86="","",IF(E86="Interno","Interno",IF(K86=0,"Sem horas",IF(L86&gt;N(F86),"Consome mais do que paga",IF(AND(N(G86)&gt;0,K86/G86&gt;1),"Estourou as horas",IF(AND(N(F86)&gt;0,(F86-L86)/F86&lt;0.2),"Margem baixa",IF(AND(N(G86)&gt;0,K86/G86&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="41" t="n"/>
@@ -7957,6 +8971,18 @@
       <c r="G87" s="46" t="n"/>
       <c r="H87" s="47" t="n"/>
       <c r="I87" s="42" t="n"/>
+      <c r="K87" s="39">
+        <f>IF(A87="","",N(H87)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A87))</f>
+        <v/>
+      </c>
+      <c r="L87" s="39">
+        <f>IF(A87="","",N(H87)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A87))</f>
+        <v/>
+      </c>
+      <c r="M87" s="39">
+        <f>IF(A87="","",IF(E87="Interno","Interno",IF(K87=0,"Sem horas",IF(L87&gt;N(F87),"Consome mais do que paga",IF(AND(N(G87)&gt;0,K87/G87&gt;1),"Estourou as horas",IF(AND(N(F87)&gt;0,(F87-L87)/F87&lt;0.2),"Margem baixa",IF(AND(N(G87)&gt;0,K87/G87&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="41" t="n"/>
@@ -7968,6 +8994,18 @@
       <c r="G88" s="46" t="n"/>
       <c r="H88" s="47" t="n"/>
       <c r="I88" s="42" t="n"/>
+      <c r="K88" s="39">
+        <f>IF(A88="","",N(H88)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A88))</f>
+        <v/>
+      </c>
+      <c r="L88" s="39">
+        <f>IF(A88="","",N(H88)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A88))</f>
+        <v/>
+      </c>
+      <c r="M88" s="39">
+        <f>IF(A88="","",IF(E88="Interno","Interno",IF(K88=0,"Sem horas",IF(L88&gt;N(F88),"Consome mais do que paga",IF(AND(N(G88)&gt;0,K88/G88&gt;1),"Estourou as horas",IF(AND(N(F88)&gt;0,(F88-L88)/F88&lt;0.2),"Margem baixa",IF(AND(N(G88)&gt;0,K88/G88&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="41" t="n"/>
@@ -7979,6 +9017,18 @@
       <c r="G89" s="46" t="n"/>
       <c r="H89" s="47" t="n"/>
       <c r="I89" s="42" t="n"/>
+      <c r="K89" s="39">
+        <f>IF(A89="","",N(H89)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A89))</f>
+        <v/>
+      </c>
+      <c r="L89" s="39">
+        <f>IF(A89="","",N(H89)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A89))</f>
+        <v/>
+      </c>
+      <c r="M89" s="39">
+        <f>IF(A89="","",IF(E89="Interno","Interno",IF(K89=0,"Sem horas",IF(L89&gt;N(F89),"Consome mais do que paga",IF(AND(N(G89)&gt;0,K89/G89&gt;1),"Estourou as horas",IF(AND(N(F89)&gt;0,(F89-L89)/F89&lt;0.2),"Margem baixa",IF(AND(N(G89)&gt;0,K89/G89&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="41" t="n"/>
@@ -7990,6 +9040,18 @@
       <c r="G90" s="46" t="n"/>
       <c r="H90" s="47" t="n"/>
       <c r="I90" s="42" t="n"/>
+      <c r="K90" s="39">
+        <f>IF(A90="","",N(H90)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A90))</f>
+        <v/>
+      </c>
+      <c r="L90" s="39">
+        <f>IF(A90="","",N(H90)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A90))</f>
+        <v/>
+      </c>
+      <c r="M90" s="39">
+        <f>IF(A90="","",IF(E90="Interno","Interno",IF(K90=0,"Sem horas",IF(L90&gt;N(F90),"Consome mais do que paga",IF(AND(N(G90)&gt;0,K90/G90&gt;1),"Estourou as horas",IF(AND(N(F90)&gt;0,(F90-L90)/F90&lt;0.2),"Margem baixa",IF(AND(N(G90)&gt;0,K90/G90&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="41" t="n"/>
@@ -8001,6 +9063,18 @@
       <c r="G91" s="46" t="n"/>
       <c r="H91" s="47" t="n"/>
       <c r="I91" s="42" t="n"/>
+      <c r="K91" s="39">
+        <f>IF(A91="","",N(H91)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A91))</f>
+        <v/>
+      </c>
+      <c r="L91" s="39">
+        <f>IF(A91="","",N(H91)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A91))</f>
+        <v/>
+      </c>
+      <c r="M91" s="39">
+        <f>IF(A91="","",IF(E91="Interno","Interno",IF(K91=0,"Sem horas",IF(L91&gt;N(F91),"Consome mais do que paga",IF(AND(N(G91)&gt;0,K91/G91&gt;1),"Estourou as horas",IF(AND(N(F91)&gt;0,(F91-L91)/F91&lt;0.2),"Margem baixa",IF(AND(N(G91)&gt;0,K91/G91&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="41" t="n"/>
@@ -8012,6 +9086,18 @@
       <c r="G92" s="46" t="n"/>
       <c r="H92" s="47" t="n"/>
       <c r="I92" s="42" t="n"/>
+      <c r="K92" s="39">
+        <f>IF(A92="","",N(H92)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A92))</f>
+        <v/>
+      </c>
+      <c r="L92" s="39">
+        <f>IF(A92="","",N(H92)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A92))</f>
+        <v/>
+      </c>
+      <c r="M92" s="39">
+        <f>IF(A92="","",IF(E92="Interno","Interno",IF(K92=0,"Sem horas",IF(L92&gt;N(F92),"Consome mais do que paga",IF(AND(N(G92)&gt;0,K92/G92&gt;1),"Estourou as horas",IF(AND(N(F92)&gt;0,(F92-L92)/F92&lt;0.2),"Margem baixa",IF(AND(N(G92)&gt;0,K92/G92&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="41" t="n"/>
@@ -8023,6 +9109,18 @@
       <c r="G93" s="46" t="n"/>
       <c r="H93" s="47" t="n"/>
       <c r="I93" s="42" t="n"/>
+      <c r="K93" s="39">
+        <f>IF(A93="","",N(H93)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A93))</f>
+        <v/>
+      </c>
+      <c r="L93" s="39">
+        <f>IF(A93="","",N(H93)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A93))</f>
+        <v/>
+      </c>
+      <c r="M93" s="39">
+        <f>IF(A93="","",IF(E93="Interno","Interno",IF(K93=0,"Sem horas",IF(L93&gt;N(F93),"Consome mais do que paga",IF(AND(N(G93)&gt;0,K93/G93&gt;1),"Estourou as horas",IF(AND(N(F93)&gt;0,(F93-L93)/F93&lt;0.2),"Margem baixa",IF(AND(N(G93)&gt;0,K93/G93&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="41" t="n"/>
@@ -8034,6 +9132,18 @@
       <c r="G94" s="46" t="n"/>
       <c r="H94" s="47" t="n"/>
       <c r="I94" s="42" t="n"/>
+      <c r="K94" s="39">
+        <f>IF(A94="","",N(H94)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A94))</f>
+        <v/>
+      </c>
+      <c r="L94" s="39">
+        <f>IF(A94="","",N(H94)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A94))</f>
+        <v/>
+      </c>
+      <c r="M94" s="39">
+        <f>IF(A94="","",IF(E94="Interno","Interno",IF(K94=0,"Sem horas",IF(L94&gt;N(F94),"Consome mais do que paga",IF(AND(N(G94)&gt;0,K94/G94&gt;1),"Estourou as horas",IF(AND(N(F94)&gt;0,(F94-L94)/F94&lt;0.2),"Margem baixa",IF(AND(N(G94)&gt;0,K94/G94&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="41" t="n"/>
@@ -8045,6 +9155,18 @@
       <c r="G95" s="46" t="n"/>
       <c r="H95" s="47" t="n"/>
       <c r="I95" s="42" t="n"/>
+      <c r="K95" s="39">
+        <f>IF(A95="","",N(H95)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A95))</f>
+        <v/>
+      </c>
+      <c r="L95" s="39">
+        <f>IF(A95="","",N(H95)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A95))</f>
+        <v/>
+      </c>
+      <c r="M95" s="39">
+        <f>IF(A95="","",IF(E95="Interno","Interno",IF(K95=0,"Sem horas",IF(L95&gt;N(F95),"Consome mais do que paga",IF(AND(N(G95)&gt;0,K95/G95&gt;1),"Estourou as horas",IF(AND(N(F95)&gt;0,(F95-L95)/F95&lt;0.2),"Margem baixa",IF(AND(N(G95)&gt;0,K95/G95&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="41" t="n"/>
@@ -8056,6 +9178,18 @@
       <c r="G96" s="46" t="n"/>
       <c r="H96" s="47" t="n"/>
       <c r="I96" s="42" t="n"/>
+      <c r="K96" s="39">
+        <f>IF(A96="","",N(H96)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A96))</f>
+        <v/>
+      </c>
+      <c r="L96" s="39">
+        <f>IF(A96="","",N(H96)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A96))</f>
+        <v/>
+      </c>
+      <c r="M96" s="39">
+        <f>IF(A96="","",IF(E96="Interno","Interno",IF(K96=0,"Sem horas",IF(L96&gt;N(F96),"Consome mais do que paga",IF(AND(N(G96)&gt;0,K96/G96&gt;1),"Estourou as horas",IF(AND(N(F96)&gt;0,(F96-L96)/F96&lt;0.2),"Margem baixa",IF(AND(N(G96)&gt;0,K96/G96&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="41" t="n"/>
@@ -8067,6 +9201,18 @@
       <c r="G97" s="46" t="n"/>
       <c r="H97" s="47" t="n"/>
       <c r="I97" s="42" t="n"/>
+      <c r="K97" s="39">
+        <f>IF(A97="","",N(H97)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A97))</f>
+        <v/>
+      </c>
+      <c r="L97" s="39">
+        <f>IF(A97="","",N(H97)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A97))</f>
+        <v/>
+      </c>
+      <c r="M97" s="39">
+        <f>IF(A97="","",IF(E97="Interno","Interno",IF(K97=0,"Sem horas",IF(L97&gt;N(F97),"Consome mais do que paga",IF(AND(N(G97)&gt;0,K97/G97&gt;1),"Estourou as horas",IF(AND(N(F97)&gt;0,(F97-L97)/F97&lt;0.2),"Margem baixa",IF(AND(N(G97)&gt;0,K97/G97&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="41" t="n"/>
@@ -8078,6 +9224,18 @@
       <c r="G98" s="46" t="n"/>
       <c r="H98" s="47" t="n"/>
       <c r="I98" s="42" t="n"/>
+      <c r="K98" s="39">
+        <f>IF(A98="","",N(H98)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A98))</f>
+        <v/>
+      </c>
+      <c r="L98" s="39">
+        <f>IF(A98="","",N(H98)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A98))</f>
+        <v/>
+      </c>
+      <c r="M98" s="39">
+        <f>IF(A98="","",IF(E98="Interno","Interno",IF(K98=0,"Sem horas",IF(L98&gt;N(F98),"Consome mais do que paga",IF(AND(N(G98)&gt;0,K98/G98&gt;1),"Estourou as horas",IF(AND(N(F98)&gt;0,(F98-L98)/F98&lt;0.2),"Margem baixa",IF(AND(N(G98)&gt;0,K98/G98&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="41" t="n"/>
@@ -8089,6 +9247,18 @@
       <c r="G99" s="46" t="n"/>
       <c r="H99" s="47" t="n"/>
       <c r="I99" s="42" t="n"/>
+      <c r="K99" s="39">
+        <f>IF(A99="","",N(H99)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A99))</f>
+        <v/>
+      </c>
+      <c r="L99" s="39">
+        <f>IF(A99="","",N(H99)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A99))</f>
+        <v/>
+      </c>
+      <c r="M99" s="39">
+        <f>IF(A99="","",IF(E99="Interno","Interno",IF(K99=0,"Sem horas",IF(L99&gt;N(F99),"Consome mais do que paga",IF(AND(N(G99)&gt;0,K99/G99&gt;1),"Estourou as horas",IF(AND(N(F99)&gt;0,(F99-L99)/F99&lt;0.2),"Margem baixa",IF(AND(N(G99)&gt;0,K99/G99&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="41" t="n"/>
@@ -8100,6 +9270,18 @@
       <c r="G100" s="46" t="n"/>
       <c r="H100" s="47" t="n"/>
       <c r="I100" s="42" t="n"/>
+      <c r="K100" s="39">
+        <f>IF(A100="","",N(H100)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A100))</f>
+        <v/>
+      </c>
+      <c r="L100" s="39">
+        <f>IF(A100="","",N(H100)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A100))</f>
+        <v/>
+      </c>
+      <c r="M100" s="39">
+        <f>IF(A100="","",IF(E100="Interno","Interno",IF(K100=0,"Sem horas",IF(L100&gt;N(F100),"Consome mais do que paga",IF(AND(N(G100)&gt;0,K100/G100&gt;1),"Estourou as horas",IF(AND(N(F100)&gt;0,(F100-L100)/F100&lt;0.2),"Margem baixa",IF(AND(N(G100)&gt;0,K100/G100&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="41" t="n"/>
@@ -8111,6 +9293,18 @@
       <c r="G101" s="46" t="n"/>
       <c r="H101" s="47" t="n"/>
       <c r="I101" s="42" t="n"/>
+      <c r="K101" s="39">
+        <f>IF(A101="","",N(H101)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A101))</f>
+        <v/>
+      </c>
+      <c r="L101" s="39">
+        <f>IF(A101="","",N(H101)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A101))</f>
+        <v/>
+      </c>
+      <c r="M101" s="39">
+        <f>IF(A101="","",IF(E101="Interno","Interno",IF(K101=0,"Sem horas",IF(L101&gt;N(F101),"Consome mais do que paga",IF(AND(N(G101)&gt;0,K101/G101&gt;1),"Estourou as horas",IF(AND(N(F101)&gt;0,(F101-L101)/F101&lt;0.2),"Margem baixa",IF(AND(N(G101)&gt;0,K101/G101&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="41" t="n"/>
@@ -8122,6 +9316,18 @@
       <c r="G102" s="46" t="n"/>
       <c r="H102" s="47" t="n"/>
       <c r="I102" s="42" t="n"/>
+      <c r="K102" s="39">
+        <f>IF(A102="","",N(H102)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A102))</f>
+        <v/>
+      </c>
+      <c r="L102" s="39">
+        <f>IF(A102="","",N(H102)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A102))</f>
+        <v/>
+      </c>
+      <c r="M102" s="39">
+        <f>IF(A102="","",IF(E102="Interno","Interno",IF(K102=0,"Sem horas",IF(L102&gt;N(F102),"Consome mais do que paga",IF(AND(N(G102)&gt;0,K102/G102&gt;1),"Estourou as horas",IF(AND(N(F102)&gt;0,(F102-L102)/F102&lt;0.2),"Margem baixa",IF(AND(N(G102)&gt;0,K102/G102&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="41" t="n"/>
@@ -8133,6 +9339,18 @@
       <c r="G103" s="46" t="n"/>
       <c r="H103" s="47" t="n"/>
       <c r="I103" s="42" t="n"/>
+      <c r="K103" s="39">
+        <f>IF(A103="","",N(H103)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A103))</f>
+        <v/>
+      </c>
+      <c r="L103" s="39">
+        <f>IF(A103="","",N(H103)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A103))</f>
+        <v/>
+      </c>
+      <c r="M103" s="39">
+        <f>IF(A103="","",IF(E103="Interno","Interno",IF(K103=0,"Sem horas",IF(L103&gt;N(F103),"Consome mais do que paga",IF(AND(N(G103)&gt;0,K103/G103&gt;1),"Estourou as horas",IF(AND(N(F103)&gt;0,(F103-L103)/F103&lt;0.2),"Margem baixa",IF(AND(N(G103)&gt;0,K103/G103&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="41" t="n"/>
@@ -8144,6 +9362,18 @@
       <c r="G104" s="46" t="n"/>
       <c r="H104" s="47" t="n"/>
       <c r="I104" s="42" t="n"/>
+      <c r="K104" s="39">
+        <f>IF(A104="","",N(H104)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A104))</f>
+        <v/>
+      </c>
+      <c r="L104" s="39">
+        <f>IF(A104="","",N(H104)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A104))</f>
+        <v/>
+      </c>
+      <c r="M104" s="39">
+        <f>IF(A104="","",IF(E104="Interno","Interno",IF(K104=0,"Sem horas",IF(L104&gt;N(F104),"Consome mais do que paga",IF(AND(N(G104)&gt;0,K104/G104&gt;1),"Estourou as horas",IF(AND(N(F104)&gt;0,(F104-L104)/F104&lt;0.2),"Margem baixa",IF(AND(N(G104)&gt;0,K104/G104&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="41" t="n"/>
@@ -8155,6 +9385,18 @@
       <c r="G105" s="46" t="n"/>
       <c r="H105" s="47" t="n"/>
       <c r="I105" s="42" t="n"/>
+      <c r="K105" s="39">
+        <f>IF(A105="","",N(H105)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A105))</f>
+        <v/>
+      </c>
+      <c r="L105" s="39">
+        <f>IF(A105="","",N(H105)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A105))</f>
+        <v/>
+      </c>
+      <c r="M105" s="39">
+        <f>IF(A105="","",IF(E105="Interno","Interno",IF(K105=0,"Sem horas",IF(L105&gt;N(F105),"Consome mais do que paga",IF(AND(N(G105)&gt;0,K105/G105&gt;1),"Estourou as horas",IF(AND(N(F105)&gt;0,(F105-L105)/F105&lt;0.2),"Margem baixa",IF(AND(N(G105)&gt;0,K105/G105&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="41" t="n"/>
@@ -8166,6 +9408,18 @@
       <c r="G106" s="46" t="n"/>
       <c r="H106" s="47" t="n"/>
       <c r="I106" s="42" t="n"/>
+      <c r="K106" s="39">
+        <f>IF(A106="","",N(H106)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A106))</f>
+        <v/>
+      </c>
+      <c r="L106" s="39">
+        <f>IF(A106="","",N(H106)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A106))</f>
+        <v/>
+      </c>
+      <c r="M106" s="39">
+        <f>IF(A106="","",IF(E106="Interno","Interno",IF(K106=0,"Sem horas",IF(L106&gt;N(F106),"Consome mais do que paga",IF(AND(N(G106)&gt;0,K106/G106&gt;1),"Estourou as horas",IF(AND(N(F106)&gt;0,(F106-L106)/F106&lt;0.2),"Margem baixa",IF(AND(N(G106)&gt;0,K106/G106&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="41" t="n"/>
@@ -8177,6 +9431,18 @@
       <c r="G107" s="46" t="n"/>
       <c r="H107" s="47" t="n"/>
       <c r="I107" s="42" t="n"/>
+      <c r="K107" s="39">
+        <f>IF(A107="","",N(H107)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A107))</f>
+        <v/>
+      </c>
+      <c r="L107" s="39">
+        <f>IF(A107="","",N(H107)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A107))</f>
+        <v/>
+      </c>
+      <c r="M107" s="39">
+        <f>IF(A107="","",IF(E107="Interno","Interno",IF(K107=0,"Sem horas",IF(L107&gt;N(F107),"Consome mais do que paga",IF(AND(N(G107)&gt;0,K107/G107&gt;1),"Estourou as horas",IF(AND(N(F107)&gt;0,(F107-L107)/F107&lt;0.2),"Margem baixa",IF(AND(N(G107)&gt;0,K107/G107&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="41" t="n"/>
@@ -8188,6 +9454,18 @@
       <c r="G108" s="46" t="n"/>
       <c r="H108" s="47" t="n"/>
       <c r="I108" s="42" t="n"/>
+      <c r="K108" s="39">
+        <f>IF(A108="","",N(H108)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A108))</f>
+        <v/>
+      </c>
+      <c r="L108" s="39">
+        <f>IF(A108="","",N(H108)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A108))</f>
+        <v/>
+      </c>
+      <c r="M108" s="39">
+        <f>IF(A108="","",IF(E108="Interno","Interno",IF(K108=0,"Sem horas",IF(L108&gt;N(F108),"Consome mais do que paga",IF(AND(N(G108)&gt;0,K108/G108&gt;1),"Estourou as horas",IF(AND(N(F108)&gt;0,(F108-L108)/F108&lt;0.2),"Margem baixa",IF(AND(N(G108)&gt;0,K108/G108&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="41" t="n"/>
@@ -8199,6 +9477,18 @@
       <c r="G109" s="46" t="n"/>
       <c r="H109" s="47" t="n"/>
       <c r="I109" s="42" t="n"/>
+      <c r="K109" s="39">
+        <f>IF(A109="","",N(H109)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A109))</f>
+        <v/>
+      </c>
+      <c r="L109" s="39">
+        <f>IF(A109="","",N(H109)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A109))</f>
+        <v/>
+      </c>
+      <c r="M109" s="39">
+        <f>IF(A109="","",IF(E109="Interno","Interno",IF(K109=0,"Sem horas",IF(L109&gt;N(F109),"Consome mais do que paga",IF(AND(N(G109)&gt;0,K109/G109&gt;1),"Estourou as horas",IF(AND(N(F109)&gt;0,(F109-L109)/F109&lt;0.2),"Margem baixa",IF(AND(N(G109)&gt;0,K109/G109&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="41" t="n"/>
@@ -8210,6 +9500,18 @@
       <c r="G110" s="46" t="n"/>
       <c r="H110" s="47" t="n"/>
       <c r="I110" s="42" t="n"/>
+      <c r="K110" s="39">
+        <f>IF(A110="","",N(H110)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A110))</f>
+        <v/>
+      </c>
+      <c r="L110" s="39">
+        <f>IF(A110="","",N(H110)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A110))</f>
+        <v/>
+      </c>
+      <c r="M110" s="39">
+        <f>IF(A110="","",IF(E110="Interno","Interno",IF(K110=0,"Sem horas",IF(L110&gt;N(F110),"Consome mais do que paga",IF(AND(N(G110)&gt;0,K110/G110&gt;1),"Estourou as horas",IF(AND(N(F110)&gt;0,(F110-L110)/F110&lt;0.2),"Margem baixa",IF(AND(N(G110)&gt;0,K110/G110&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="41" t="n"/>
@@ -8221,6 +9523,18 @@
       <c r="G111" s="46" t="n"/>
       <c r="H111" s="47" t="n"/>
       <c r="I111" s="42" t="n"/>
+      <c r="K111" s="39">
+        <f>IF(A111="","",N(H111)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A111))</f>
+        <v/>
+      </c>
+      <c r="L111" s="39">
+        <f>IF(A111="","",N(H111)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A111))</f>
+        <v/>
+      </c>
+      <c r="M111" s="39">
+        <f>IF(A111="","",IF(E111="Interno","Interno",IF(K111=0,"Sem horas",IF(L111&gt;N(F111),"Consome mais do que paga",IF(AND(N(G111)&gt;0,K111/G111&gt;1),"Estourou as horas",IF(AND(N(F111)&gt;0,(F111-L111)/F111&lt;0.2),"Margem baixa",IF(AND(N(G111)&gt;0,K111/G111&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="41" t="n"/>
@@ -8232,6 +9546,18 @@
       <c r="G112" s="46" t="n"/>
       <c r="H112" s="47" t="n"/>
       <c r="I112" s="42" t="n"/>
+      <c r="K112" s="39">
+        <f>IF(A112="","",N(H112)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A112))</f>
+        <v/>
+      </c>
+      <c r="L112" s="39">
+        <f>IF(A112="","",N(H112)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A112))</f>
+        <v/>
+      </c>
+      <c r="M112" s="39">
+        <f>IF(A112="","",IF(E112="Interno","Interno",IF(K112=0,"Sem horas",IF(L112&gt;N(F112),"Consome mais do que paga",IF(AND(N(G112)&gt;0,K112/G112&gt;1),"Estourou as horas",IF(AND(N(F112)&gt;0,(F112-L112)/F112&lt;0.2),"Margem baixa",IF(AND(N(G112)&gt;0,K112/G112&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="41" t="n"/>
@@ -8243,6 +9569,18 @@
       <c r="G113" s="46" t="n"/>
       <c r="H113" s="47" t="n"/>
       <c r="I113" s="42" t="n"/>
+      <c r="K113" s="39">
+        <f>IF(A113="","",N(H113)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A113))</f>
+        <v/>
+      </c>
+      <c r="L113" s="39">
+        <f>IF(A113="","",N(H113)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A113))</f>
+        <v/>
+      </c>
+      <c r="M113" s="39">
+        <f>IF(A113="","",IF(E113="Interno","Interno",IF(K113=0,"Sem horas",IF(L113&gt;N(F113),"Consome mais do que paga",IF(AND(N(G113)&gt;0,K113/G113&gt;1),"Estourou as horas",IF(AND(N(F113)&gt;0,(F113-L113)/F113&lt;0.2),"Margem baixa",IF(AND(N(G113)&gt;0,K113/G113&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="41" t="n"/>
@@ -8254,6 +9592,18 @@
       <c r="G114" s="46" t="n"/>
       <c r="H114" s="47" t="n"/>
       <c r="I114" s="42" t="n"/>
+      <c r="K114" s="39">
+        <f>IF(A114="","",N(H114)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A114))</f>
+        <v/>
+      </c>
+      <c r="L114" s="39">
+        <f>IF(A114="","",N(H114)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A114))</f>
+        <v/>
+      </c>
+      <c r="M114" s="39">
+        <f>IF(A114="","",IF(E114="Interno","Interno",IF(K114=0,"Sem horas",IF(L114&gt;N(F114),"Consome mais do que paga",IF(AND(N(G114)&gt;0,K114/G114&gt;1),"Estourou as horas",IF(AND(N(F114)&gt;0,(F114-L114)/F114&lt;0.2),"Margem baixa",IF(AND(N(G114)&gt;0,K114/G114&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="41" t="n"/>
@@ -8265,6 +9615,18 @@
       <c r="G115" s="46" t="n"/>
       <c r="H115" s="47" t="n"/>
       <c r="I115" s="42" t="n"/>
+      <c r="K115" s="39">
+        <f>IF(A115="","",N(H115)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A115))</f>
+        <v/>
+      </c>
+      <c r="L115" s="39">
+        <f>IF(A115="","",N(H115)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A115))</f>
+        <v/>
+      </c>
+      <c r="M115" s="39">
+        <f>IF(A115="","",IF(E115="Interno","Interno",IF(K115=0,"Sem horas",IF(L115&gt;N(F115),"Consome mais do que paga",IF(AND(N(G115)&gt;0,K115/G115&gt;1),"Estourou as horas",IF(AND(N(F115)&gt;0,(F115-L115)/F115&lt;0.2),"Margem baixa",IF(AND(N(G115)&gt;0,K115/G115&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="41" t="n"/>
@@ -8276,6 +9638,18 @@
       <c r="G116" s="46" t="n"/>
       <c r="H116" s="47" t="n"/>
       <c r="I116" s="42" t="n"/>
+      <c r="K116" s="39">
+        <f>IF(A116="","",N(H116)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A116))</f>
+        <v/>
+      </c>
+      <c r="L116" s="39">
+        <f>IF(A116="","",N(H116)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A116))</f>
+        <v/>
+      </c>
+      <c r="M116" s="39">
+        <f>IF(A116="","",IF(E116="Interno","Interno",IF(K116=0,"Sem horas",IF(L116&gt;N(F116),"Consome mais do que paga",IF(AND(N(G116)&gt;0,K116/G116&gt;1),"Estourou as horas",IF(AND(N(F116)&gt;0,(F116-L116)/F116&lt;0.2),"Margem baixa",IF(AND(N(G116)&gt;0,K116/G116&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="41" t="n"/>
@@ -8287,6 +9661,18 @@
       <c r="G117" s="46" t="n"/>
       <c r="H117" s="47" t="n"/>
       <c r="I117" s="42" t="n"/>
+      <c r="K117" s="39">
+        <f>IF(A117="","",N(H117)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A117))</f>
+        <v/>
+      </c>
+      <c r="L117" s="39">
+        <f>IF(A117="","",N(H117)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A117))</f>
+        <v/>
+      </c>
+      <c r="M117" s="39">
+        <f>IF(A117="","",IF(E117="Interno","Interno",IF(K117=0,"Sem horas",IF(L117&gt;N(F117),"Consome mais do que paga",IF(AND(N(G117)&gt;0,K117/G117&gt;1),"Estourou as horas",IF(AND(N(F117)&gt;0,(F117-L117)/F117&lt;0.2),"Margem baixa",IF(AND(N(G117)&gt;0,K117/G117&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="41" t="n"/>
@@ -8298,6 +9684,18 @@
       <c r="G118" s="46" t="n"/>
       <c r="H118" s="47" t="n"/>
       <c r="I118" s="42" t="n"/>
+      <c r="K118" s="39">
+        <f>IF(A118="","",N(H118)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A118))</f>
+        <v/>
+      </c>
+      <c r="L118" s="39">
+        <f>IF(A118="","",N(H118)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A118))</f>
+        <v/>
+      </c>
+      <c r="M118" s="39">
+        <f>IF(A118="","",IF(E118="Interno","Interno",IF(K118=0,"Sem horas",IF(L118&gt;N(F118),"Consome mais do que paga",IF(AND(N(G118)&gt;0,K118/G118&gt;1),"Estourou as horas",IF(AND(N(F118)&gt;0,(F118-L118)/F118&lt;0.2),"Margem baixa",IF(AND(N(G118)&gt;0,K118/G118&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="41" t="n"/>
@@ -8309,6 +9707,18 @@
       <c r="G119" s="46" t="n"/>
       <c r="H119" s="47" t="n"/>
       <c r="I119" s="42" t="n"/>
+      <c r="K119" s="39">
+        <f>IF(A119="","",N(H119)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A119))</f>
+        <v/>
+      </c>
+      <c r="L119" s="39">
+        <f>IF(A119="","",N(H119)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A119))</f>
+        <v/>
+      </c>
+      <c r="M119" s="39">
+        <f>IF(A119="","",IF(E119="Interno","Interno",IF(K119=0,"Sem horas",IF(L119&gt;N(F119),"Consome mais do que paga",IF(AND(N(G119)&gt;0,K119/G119&gt;1),"Estourou as horas",IF(AND(N(F119)&gt;0,(F119-L119)/F119&lt;0.2),"Margem baixa",IF(AND(N(G119)&gt;0,K119/G119&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="41" t="n"/>
@@ -8320,6 +9730,18 @@
       <c r="G120" s="46" t="n"/>
       <c r="H120" s="47" t="n"/>
       <c r="I120" s="42" t="n"/>
+      <c r="K120" s="39">
+        <f>IF(A120="","",N(H120)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A120))</f>
+        <v/>
+      </c>
+      <c r="L120" s="39">
+        <f>IF(A120="","",N(H120)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A120))</f>
+        <v/>
+      </c>
+      <c r="M120" s="39">
+        <f>IF(A120="","",IF(E120="Interno","Interno",IF(K120=0,"Sem horas",IF(L120&gt;N(F120),"Consome mais do que paga",IF(AND(N(G120)&gt;0,K120/G120&gt;1),"Estourou as horas",IF(AND(N(F120)&gt;0,(F120-L120)/F120&lt;0.2),"Margem baixa",IF(AND(N(G120)&gt;0,K120/G120&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="41" t="n"/>
@@ -8331,6 +9753,18 @@
       <c r="G121" s="46" t="n"/>
       <c r="H121" s="47" t="n"/>
       <c r="I121" s="42" t="n"/>
+      <c r="K121" s="39">
+        <f>IF(A121="","",N(H121)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A121))</f>
+        <v/>
+      </c>
+      <c r="L121" s="39">
+        <f>IF(A121="","",N(H121)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A121))</f>
+        <v/>
+      </c>
+      <c r="M121" s="39">
+        <f>IF(A121="","",IF(E121="Interno","Interno",IF(K121=0,"Sem horas",IF(L121&gt;N(F121),"Consome mais do que paga",IF(AND(N(G121)&gt;0,K121/G121&gt;1),"Estourou as horas",IF(AND(N(F121)&gt;0,(F121-L121)/F121&lt;0.2),"Margem baixa",IF(AND(N(G121)&gt;0,K121/G121&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="41" t="n"/>
@@ -8342,6 +9776,18 @@
       <c r="G122" s="46" t="n"/>
       <c r="H122" s="47" t="n"/>
       <c r="I122" s="42" t="n"/>
+      <c r="K122" s="39">
+        <f>IF(A122="","",N(H122)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A122))</f>
+        <v/>
+      </c>
+      <c r="L122" s="39">
+        <f>IF(A122="","",N(H122)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A122))</f>
+        <v/>
+      </c>
+      <c r="M122" s="39">
+        <f>IF(A122="","",IF(E122="Interno","Interno",IF(K122=0,"Sem horas",IF(L122&gt;N(F122),"Consome mais do que paga",IF(AND(N(G122)&gt;0,K122/G122&gt;1),"Estourou as horas",IF(AND(N(F122)&gt;0,(F122-L122)/F122&lt;0.2),"Margem baixa",IF(AND(N(G122)&gt;0,K122/G122&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="41" t="n"/>
@@ -8353,6 +9799,18 @@
       <c r="G123" s="46" t="n"/>
       <c r="H123" s="47" t="n"/>
       <c r="I123" s="42" t="n"/>
+      <c r="K123" s="39">
+        <f>IF(A123="","",N(H123)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A123))</f>
+        <v/>
+      </c>
+      <c r="L123" s="39">
+        <f>IF(A123="","",N(H123)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A123))</f>
+        <v/>
+      </c>
+      <c r="M123" s="39">
+        <f>IF(A123="","",IF(E123="Interno","Interno",IF(K123=0,"Sem horas",IF(L123&gt;N(F123),"Consome mais do que paga",IF(AND(N(G123)&gt;0,K123/G123&gt;1),"Estourou as horas",IF(AND(N(F123)&gt;0,(F123-L123)/F123&lt;0.2),"Margem baixa",IF(AND(N(G123)&gt;0,K123/G123&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="41" t="n"/>
@@ -8364,6 +9822,18 @@
       <c r="G124" s="46" t="n"/>
       <c r="H124" s="47" t="n"/>
       <c r="I124" s="42" t="n"/>
+      <c r="K124" s="39">
+        <f>IF(A124="","",N(H124)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A124))</f>
+        <v/>
+      </c>
+      <c r="L124" s="39">
+        <f>IF(A124="","",N(H124)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A124))</f>
+        <v/>
+      </c>
+      <c r="M124" s="39">
+        <f>IF(A124="","",IF(E124="Interno","Interno",IF(K124=0,"Sem horas",IF(L124&gt;N(F124),"Consome mais do que paga",IF(AND(N(G124)&gt;0,K124/G124&gt;1),"Estourou as horas",IF(AND(N(F124)&gt;0,(F124-L124)/F124&lt;0.2),"Margem baixa",IF(AND(N(G124)&gt;0,K124/G124&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="41" t="n"/>
@@ -8375,6 +9845,18 @@
       <c r="G125" s="46" t="n"/>
       <c r="H125" s="47" t="n"/>
       <c r="I125" s="42" t="n"/>
+      <c r="K125" s="39">
+        <f>IF(A125="","",N(H125)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A125))</f>
+        <v/>
+      </c>
+      <c r="L125" s="39">
+        <f>IF(A125="","",N(H125)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A125))</f>
+        <v/>
+      </c>
+      <c r="M125" s="39">
+        <f>IF(A125="","",IF(E125="Interno","Interno",IF(K125=0,"Sem horas",IF(L125&gt;N(F125),"Consome mais do que paga",IF(AND(N(G125)&gt;0,K125/G125&gt;1),"Estourou as horas",IF(AND(N(F125)&gt;0,(F125-L125)/F125&lt;0.2),"Margem baixa",IF(AND(N(G125)&gt;0,K125/G125&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="41" t="n"/>
@@ -8386,6 +9868,18 @@
       <c r="G126" s="46" t="n"/>
       <c r="H126" s="47" t="n"/>
       <c r="I126" s="42" t="n"/>
+      <c r="K126" s="39">
+        <f>IF(A126="","",N(H126)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A126))</f>
+        <v/>
+      </c>
+      <c r="L126" s="39">
+        <f>IF(A126="","",N(H126)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A126))</f>
+        <v/>
+      </c>
+      <c r="M126" s="39">
+        <f>IF(A126="","",IF(E126="Interno","Interno",IF(K126=0,"Sem horas",IF(L126&gt;N(F126),"Consome mais do que paga",IF(AND(N(G126)&gt;0,K126/G126&gt;1),"Estourou as horas",IF(AND(N(F126)&gt;0,(F126-L126)/F126&lt;0.2),"Margem baixa",IF(AND(N(G126)&gt;0,K126/G126&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="41" t="n"/>
@@ -8397,6 +9891,18 @@
       <c r="G127" s="46" t="n"/>
       <c r="H127" s="47" t="n"/>
       <c r="I127" s="42" t="n"/>
+      <c r="K127" s="39">
+        <f>IF(A127="","",N(H127)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A127))</f>
+        <v/>
+      </c>
+      <c r="L127" s="39">
+        <f>IF(A127="","",N(H127)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A127))</f>
+        <v/>
+      </c>
+      <c r="M127" s="39">
+        <f>IF(A127="","",IF(E127="Interno","Interno",IF(K127=0,"Sem horas",IF(L127&gt;N(F127),"Consome mais do que paga",IF(AND(N(G127)&gt;0,K127/G127&gt;1),"Estourou as horas",IF(AND(N(F127)&gt;0,(F127-L127)/F127&lt;0.2),"Margem baixa",IF(AND(N(G127)&gt;0,K127/G127&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="41" t="n"/>
@@ -8408,6 +9914,18 @@
       <c r="G128" s="46" t="n"/>
       <c r="H128" s="47" t="n"/>
       <c r="I128" s="42" t="n"/>
+      <c r="K128" s="39">
+        <f>IF(A128="","",N(H128)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A128))</f>
+        <v/>
+      </c>
+      <c r="L128" s="39">
+        <f>IF(A128="","",N(H128)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A128))</f>
+        <v/>
+      </c>
+      <c r="M128" s="39">
+        <f>IF(A128="","",IF(E128="Interno","Interno",IF(K128=0,"Sem horas",IF(L128&gt;N(F128),"Consome mais do que paga",IF(AND(N(G128)&gt;0,K128/G128&gt;1),"Estourou as horas",IF(AND(N(F128)&gt;0,(F128-L128)/F128&lt;0.2),"Margem baixa",IF(AND(N(G128)&gt;0,K128/G128&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="41" t="n"/>
@@ -8419,6 +9937,18 @@
       <c r="G129" s="46" t="n"/>
       <c r="H129" s="47" t="n"/>
       <c r="I129" s="42" t="n"/>
+      <c r="K129" s="39">
+        <f>IF(A129="","",N(H129)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A129))</f>
+        <v/>
+      </c>
+      <c r="L129" s="39">
+        <f>IF(A129="","",N(H129)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A129))</f>
+        <v/>
+      </c>
+      <c r="M129" s="39">
+        <f>IF(A129="","",IF(E129="Interno","Interno",IF(K129=0,"Sem horas",IF(L129&gt;N(F129),"Consome mais do que paga",IF(AND(N(G129)&gt;0,K129/G129&gt;1),"Estourou as horas",IF(AND(N(F129)&gt;0,(F129-L129)/F129&lt;0.2),"Margem baixa",IF(AND(N(G129)&gt;0,K129/G129&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="41" t="n"/>
@@ -8430,6 +9960,18 @@
       <c r="G130" s="46" t="n"/>
       <c r="H130" s="47" t="n"/>
       <c r="I130" s="42" t="n"/>
+      <c r="K130" s="39">
+        <f>IF(A130="","",N(H130)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A130))</f>
+        <v/>
+      </c>
+      <c r="L130" s="39">
+        <f>IF(A130="","",N(H130)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A130))</f>
+        <v/>
+      </c>
+      <c r="M130" s="39">
+        <f>IF(A130="","",IF(E130="Interno","Interno",IF(K130=0,"Sem horas",IF(L130&gt;N(F130),"Consome mais do que paga",IF(AND(N(G130)&gt;0,K130/G130&gt;1),"Estourou as horas",IF(AND(N(F130)&gt;0,(F130-L130)/F130&lt;0.2),"Margem baixa",IF(AND(N(G130)&gt;0,K130/G130&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="41" t="n"/>
@@ -8441,6 +9983,18 @@
       <c r="G131" s="46" t="n"/>
       <c r="H131" s="47" t="n"/>
       <c r="I131" s="42" t="n"/>
+      <c r="K131" s="39">
+        <f>IF(A131="","",N(H131)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A131))</f>
+        <v/>
+      </c>
+      <c r="L131" s="39">
+        <f>IF(A131="","",N(H131)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A131))</f>
+        <v/>
+      </c>
+      <c r="M131" s="39">
+        <f>IF(A131="","",IF(E131="Interno","Interno",IF(K131=0,"Sem horas",IF(L131&gt;N(F131),"Consome mais do que paga",IF(AND(N(G131)&gt;0,K131/G131&gt;1),"Estourou as horas",IF(AND(N(F131)&gt;0,(F131-L131)/F131&lt;0.2),"Margem baixa",IF(AND(N(G131)&gt;0,K131/G131&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="41" t="n"/>
@@ -8452,6 +10006,18 @@
       <c r="G132" s="46" t="n"/>
       <c r="H132" s="47" t="n"/>
       <c r="I132" s="42" t="n"/>
+      <c r="K132" s="39">
+        <f>IF(A132="","",N(H132)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A132))</f>
+        <v/>
+      </c>
+      <c r="L132" s="39">
+        <f>IF(A132="","",N(H132)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A132))</f>
+        <v/>
+      </c>
+      <c r="M132" s="39">
+        <f>IF(A132="","",IF(E132="Interno","Interno",IF(K132=0,"Sem horas",IF(L132&gt;N(F132),"Consome mais do que paga",IF(AND(N(G132)&gt;0,K132/G132&gt;1),"Estourou as horas",IF(AND(N(F132)&gt;0,(F132-L132)/F132&lt;0.2),"Margem baixa",IF(AND(N(G132)&gt;0,K132/G132&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="41" t="n"/>
@@ -8463,6 +10029,18 @@
       <c r="G133" s="46" t="n"/>
       <c r="H133" s="47" t="n"/>
       <c r="I133" s="42" t="n"/>
+      <c r="K133" s="39">
+        <f>IF(A133="","",N(H133)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A133))</f>
+        <v/>
+      </c>
+      <c r="L133" s="39">
+        <f>IF(A133="","",N(H133)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A133))</f>
+        <v/>
+      </c>
+      <c r="M133" s="39">
+        <f>IF(A133="","",IF(E133="Interno","Interno",IF(K133=0,"Sem horas",IF(L133&gt;N(F133),"Consome mais do que paga",IF(AND(N(G133)&gt;0,K133/G133&gt;1),"Estourou as horas",IF(AND(N(F133)&gt;0,(F133-L133)/F133&lt;0.2),"Margem baixa",IF(AND(N(G133)&gt;0,K133/G133&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="41" t="n"/>
@@ -8474,6 +10052,18 @@
       <c r="G134" s="46" t="n"/>
       <c r="H134" s="47" t="n"/>
       <c r="I134" s="42" t="n"/>
+      <c r="K134" s="39">
+        <f>IF(A134="","",N(H134)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A134))</f>
+        <v/>
+      </c>
+      <c r="L134" s="39">
+        <f>IF(A134="","",N(H134)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A134))</f>
+        <v/>
+      </c>
+      <c r="M134" s="39">
+        <f>IF(A134="","",IF(E134="Interno","Interno",IF(K134=0,"Sem horas",IF(L134&gt;N(F134),"Consome mais do que paga",IF(AND(N(G134)&gt;0,K134/G134&gt;1),"Estourou as horas",IF(AND(N(F134)&gt;0,(F134-L134)/F134&lt;0.2),"Margem baixa",IF(AND(N(G134)&gt;0,K134/G134&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="41" t="n"/>
@@ -8485,6 +10075,18 @@
       <c r="G135" s="46" t="n"/>
       <c r="H135" s="47" t="n"/>
       <c r="I135" s="42" t="n"/>
+      <c r="K135" s="39">
+        <f>IF(A135="","",N(H135)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A135))</f>
+        <v/>
+      </c>
+      <c r="L135" s="39">
+        <f>IF(A135="","",N(H135)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A135))</f>
+        <v/>
+      </c>
+      <c r="M135" s="39">
+        <f>IF(A135="","",IF(E135="Interno","Interno",IF(K135=0,"Sem horas",IF(L135&gt;N(F135),"Consome mais do que paga",IF(AND(N(G135)&gt;0,K135/G135&gt;1),"Estourou as horas",IF(AND(N(F135)&gt;0,(F135-L135)/F135&lt;0.2),"Margem baixa",IF(AND(N(G135)&gt;0,K135/G135&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="41" t="n"/>
@@ -8496,6 +10098,18 @@
       <c r="G136" s="46" t="n"/>
       <c r="H136" s="47" t="n"/>
       <c r="I136" s="42" t="n"/>
+      <c r="K136" s="39">
+        <f>IF(A136="","",N(H136)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A136))</f>
+        <v/>
+      </c>
+      <c r="L136" s="39">
+        <f>IF(A136="","",N(H136)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A136))</f>
+        <v/>
+      </c>
+      <c r="M136" s="39">
+        <f>IF(A136="","",IF(E136="Interno","Interno",IF(K136=0,"Sem horas",IF(L136&gt;N(F136),"Consome mais do que paga",IF(AND(N(G136)&gt;0,K136/G136&gt;1),"Estourou as horas",IF(AND(N(F136)&gt;0,(F136-L136)/F136&lt;0.2),"Margem baixa",IF(AND(N(G136)&gt;0,K136/G136&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="41" t="n"/>
@@ -8507,6 +10121,18 @@
       <c r="G137" s="46" t="n"/>
       <c r="H137" s="47" t="n"/>
       <c r="I137" s="42" t="n"/>
+      <c r="K137" s="39">
+        <f>IF(A137="","",N(H137)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A137))</f>
+        <v/>
+      </c>
+      <c r="L137" s="39">
+        <f>IF(A137="","",N(H137)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A137))</f>
+        <v/>
+      </c>
+      <c r="M137" s="39">
+        <f>IF(A137="","",IF(E137="Interno","Interno",IF(K137=0,"Sem horas",IF(L137&gt;N(F137),"Consome mais do que paga",IF(AND(N(G137)&gt;0,K137/G137&gt;1),"Estourou as horas",IF(AND(N(F137)&gt;0,(F137-L137)/F137&lt;0.2),"Margem baixa",IF(AND(N(G137)&gt;0,K137/G137&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="41" t="n"/>
@@ -8518,6 +10144,18 @@
       <c r="G138" s="46" t="n"/>
       <c r="H138" s="47" t="n"/>
       <c r="I138" s="42" t="n"/>
+      <c r="K138" s="39">
+        <f>IF(A138="","",N(H138)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A138))</f>
+        <v/>
+      </c>
+      <c r="L138" s="39">
+        <f>IF(A138="","",N(H138)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A138))</f>
+        <v/>
+      </c>
+      <c r="M138" s="39">
+        <f>IF(A138="","",IF(E138="Interno","Interno",IF(K138=0,"Sem horas",IF(L138&gt;N(F138),"Consome mais do que paga",IF(AND(N(G138)&gt;0,K138/G138&gt;1),"Estourou as horas",IF(AND(N(F138)&gt;0,(F138-L138)/F138&lt;0.2),"Margem baixa",IF(AND(N(G138)&gt;0,K138/G138&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="41" t="n"/>
@@ -8529,6 +10167,18 @@
       <c r="G139" s="46" t="n"/>
       <c r="H139" s="47" t="n"/>
       <c r="I139" s="42" t="n"/>
+      <c r="K139" s="39">
+        <f>IF(A139="","",N(H139)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A139))</f>
+        <v/>
+      </c>
+      <c r="L139" s="39">
+        <f>IF(A139="","",N(H139)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A139))</f>
+        <v/>
+      </c>
+      <c r="M139" s="39">
+        <f>IF(A139="","",IF(E139="Interno","Interno",IF(K139=0,"Sem horas",IF(L139&gt;N(F139),"Consome mais do que paga",IF(AND(N(G139)&gt;0,K139/G139&gt;1),"Estourou as horas",IF(AND(N(F139)&gt;0,(F139-L139)/F139&lt;0.2),"Margem baixa",IF(AND(N(G139)&gt;0,K139/G139&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="41" t="n"/>
@@ -8540,6 +10190,18 @@
       <c r="G140" s="46" t="n"/>
       <c r="H140" s="47" t="n"/>
       <c r="I140" s="42" t="n"/>
+      <c r="K140" s="39">
+        <f>IF(A140="","",N(H140)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A140))</f>
+        <v/>
+      </c>
+      <c r="L140" s="39">
+        <f>IF(A140="","",N(H140)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A140))</f>
+        <v/>
+      </c>
+      <c r="M140" s="39">
+        <f>IF(A140="","",IF(E140="Interno","Interno",IF(K140=0,"Sem horas",IF(L140&gt;N(F140),"Consome mais do que paga",IF(AND(N(G140)&gt;0,K140/G140&gt;1),"Estourou as horas",IF(AND(N(F140)&gt;0,(F140-L140)/F140&lt;0.2),"Margem baixa",IF(AND(N(G140)&gt;0,K140/G140&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="41" t="n"/>
@@ -8551,6 +10213,18 @@
       <c r="G141" s="46" t="n"/>
       <c r="H141" s="47" t="n"/>
       <c r="I141" s="42" t="n"/>
+      <c r="K141" s="39">
+        <f>IF(A141="","",N(H141)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A141))</f>
+        <v/>
+      </c>
+      <c r="L141" s="39">
+        <f>IF(A141="","",N(H141)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A141))</f>
+        <v/>
+      </c>
+      <c r="M141" s="39">
+        <f>IF(A141="","",IF(E141="Interno","Interno",IF(K141=0,"Sem horas",IF(L141&gt;N(F141),"Consome mais do que paga",IF(AND(N(G141)&gt;0,K141/G141&gt;1),"Estourou as horas",IF(AND(N(F141)&gt;0,(F141-L141)/F141&lt;0.2),"Margem baixa",IF(AND(N(G141)&gt;0,K141/G141&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="41" t="n"/>
@@ -8562,6 +10236,18 @@
       <c r="G142" s="46" t="n"/>
       <c r="H142" s="47" t="n"/>
       <c r="I142" s="42" t="n"/>
+      <c r="K142" s="39">
+        <f>IF(A142="","",N(H142)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A142))</f>
+        <v/>
+      </c>
+      <c r="L142" s="39">
+        <f>IF(A142="","",N(H142)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A142))</f>
+        <v/>
+      </c>
+      <c r="M142" s="39">
+        <f>IF(A142="","",IF(E142="Interno","Interno",IF(K142=0,"Sem horas",IF(L142&gt;N(F142),"Consome mais do que paga",IF(AND(N(G142)&gt;0,K142/G142&gt;1),"Estourou as horas",IF(AND(N(F142)&gt;0,(F142-L142)/F142&lt;0.2),"Margem baixa",IF(AND(N(G142)&gt;0,K142/G142&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="41" t="n"/>
@@ -8573,6 +10259,18 @@
       <c r="G143" s="46" t="n"/>
       <c r="H143" s="47" t="n"/>
       <c r="I143" s="42" t="n"/>
+      <c r="K143" s="39">
+        <f>IF(A143="","",N(H143)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A143))</f>
+        <v/>
+      </c>
+      <c r="L143" s="39">
+        <f>IF(A143="","",N(H143)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A143))</f>
+        <v/>
+      </c>
+      <c r="M143" s="39">
+        <f>IF(A143="","",IF(E143="Interno","Interno",IF(K143=0,"Sem horas",IF(L143&gt;N(F143),"Consome mais do que paga",IF(AND(N(G143)&gt;0,K143/G143&gt;1),"Estourou as horas",IF(AND(N(F143)&gt;0,(F143-L143)/F143&lt;0.2),"Margem baixa",IF(AND(N(G143)&gt;0,K143/G143&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="41" t="n"/>
@@ -8584,6 +10282,18 @@
       <c r="G144" s="46" t="n"/>
       <c r="H144" s="47" t="n"/>
       <c r="I144" s="42" t="n"/>
+      <c r="K144" s="39">
+        <f>IF(A144="","",N(H144)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A144))</f>
+        <v/>
+      </c>
+      <c r="L144" s="39">
+        <f>IF(A144="","",N(H144)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A144))</f>
+        <v/>
+      </c>
+      <c r="M144" s="39">
+        <f>IF(A144="","",IF(E144="Interno","Interno",IF(K144=0,"Sem horas",IF(L144&gt;N(F144),"Consome mais do que paga",IF(AND(N(G144)&gt;0,K144/G144&gt;1),"Estourou as horas",IF(AND(N(F144)&gt;0,(F144-L144)/F144&lt;0.2),"Margem baixa",IF(AND(N(G144)&gt;0,K144/G144&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="41" t="n"/>
@@ -8595,6 +10305,18 @@
       <c r="G145" s="46" t="n"/>
       <c r="H145" s="47" t="n"/>
       <c r="I145" s="42" t="n"/>
+      <c r="K145" s="39">
+        <f>IF(A145="","",N(H145)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A145))</f>
+        <v/>
+      </c>
+      <c r="L145" s="39">
+        <f>IF(A145="","",N(H145)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A145))</f>
+        <v/>
+      </c>
+      <c r="M145" s="39">
+        <f>IF(A145="","",IF(E145="Interno","Interno",IF(K145=0,"Sem horas",IF(L145&gt;N(F145),"Consome mais do que paga",IF(AND(N(G145)&gt;0,K145/G145&gt;1),"Estourou as horas",IF(AND(N(F145)&gt;0,(F145-L145)/F145&lt;0.2),"Margem baixa",IF(AND(N(G145)&gt;0,K145/G145&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="41" t="n"/>
@@ -8606,6 +10328,18 @@
       <c r="G146" s="46" t="n"/>
       <c r="H146" s="47" t="n"/>
       <c r="I146" s="42" t="n"/>
+      <c r="K146" s="39">
+        <f>IF(A146="","",N(H146)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A146))</f>
+        <v/>
+      </c>
+      <c r="L146" s="39">
+        <f>IF(A146="","",N(H146)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A146))</f>
+        <v/>
+      </c>
+      <c r="M146" s="39">
+        <f>IF(A146="","",IF(E146="Interno","Interno",IF(K146=0,"Sem horas",IF(L146&gt;N(F146),"Consome mais do que paga",IF(AND(N(G146)&gt;0,K146/G146&gt;1),"Estourou as horas",IF(AND(N(F146)&gt;0,(F146-L146)/F146&lt;0.2),"Margem baixa",IF(AND(N(G146)&gt;0,K146/G146&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="41" t="n"/>
@@ -8617,6 +10351,18 @@
       <c r="G147" s="46" t="n"/>
       <c r="H147" s="47" t="n"/>
       <c r="I147" s="42" t="n"/>
+      <c r="K147" s="39">
+        <f>IF(A147="","",N(H147)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A147))</f>
+        <v/>
+      </c>
+      <c r="L147" s="39">
+        <f>IF(A147="","",N(H147)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A147))</f>
+        <v/>
+      </c>
+      <c r="M147" s="39">
+        <f>IF(A147="","",IF(E147="Interno","Interno",IF(K147=0,"Sem horas",IF(L147&gt;N(F147),"Consome mais do que paga",IF(AND(N(G147)&gt;0,K147/G147&gt;1),"Estourou as horas",IF(AND(N(F147)&gt;0,(F147-L147)/F147&lt;0.2),"Margem baixa",IF(AND(N(G147)&gt;0,K147/G147&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="41" t="n"/>
@@ -8628,6 +10374,18 @@
       <c r="G148" s="46" t="n"/>
       <c r="H148" s="47" t="n"/>
       <c r="I148" s="42" t="n"/>
+      <c r="K148" s="39">
+        <f>IF(A148="","",N(H148)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A148))</f>
+        <v/>
+      </c>
+      <c r="L148" s="39">
+        <f>IF(A148="","",N(H148)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A148))</f>
+        <v/>
+      </c>
+      <c r="M148" s="39">
+        <f>IF(A148="","",IF(E148="Interno","Interno",IF(K148=0,"Sem horas",IF(L148&gt;N(F148),"Consome mais do que paga",IF(AND(N(G148)&gt;0,K148/G148&gt;1),"Estourou as horas",IF(AND(N(F148)&gt;0,(F148-L148)/F148&lt;0.2),"Margem baixa",IF(AND(N(G148)&gt;0,K148/G148&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="41" t="n"/>
@@ -8639,6 +10397,18 @@
       <c r="G149" s="46" t="n"/>
       <c r="H149" s="47" t="n"/>
       <c r="I149" s="42" t="n"/>
+      <c r="K149" s="39">
+        <f>IF(A149="","",N(H149)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A149))</f>
+        <v/>
+      </c>
+      <c r="L149" s="39">
+        <f>IF(A149="","",N(H149)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A149))</f>
+        <v/>
+      </c>
+      <c r="M149" s="39">
+        <f>IF(A149="","",IF(E149="Interno","Interno",IF(K149=0,"Sem horas",IF(L149&gt;N(F149),"Consome mais do que paga",IF(AND(N(G149)&gt;0,K149/G149&gt;1),"Estourou as horas",IF(AND(N(F149)&gt;0,(F149-L149)/F149&lt;0.2),"Margem baixa",IF(AND(N(G149)&gt;0,K149/G149&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="41" t="n"/>
@@ -8650,6 +10420,18 @@
       <c r="G150" s="46" t="n"/>
       <c r="H150" s="47" t="n"/>
       <c r="I150" s="42" t="n"/>
+      <c r="K150" s="39">
+        <f>IF(A150="","",N(H150)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A150))</f>
+        <v/>
+      </c>
+      <c r="L150" s="39">
+        <f>IF(A150="","",N(H150)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A150))</f>
+        <v/>
+      </c>
+      <c r="M150" s="39">
+        <f>IF(A150="","",IF(E150="Interno","Interno",IF(K150=0,"Sem horas",IF(L150&gt;N(F150),"Consome mais do que paga",IF(AND(N(G150)&gt;0,K150/G150&gt;1),"Estourou as horas",IF(AND(N(F150)&gt;0,(F150-L150)/F150&lt;0.2),"Margem baixa",IF(AND(N(G150)&gt;0,K150/G150&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="41" t="n"/>
@@ -8661,6 +10443,18 @@
       <c r="G151" s="46" t="n"/>
       <c r="H151" s="47" t="n"/>
       <c r="I151" s="42" t="n"/>
+      <c r="K151" s="39">
+        <f>IF(A151="","",N(H151)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A151))</f>
+        <v/>
+      </c>
+      <c r="L151" s="39">
+        <f>IF(A151="","",N(H151)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A151))</f>
+        <v/>
+      </c>
+      <c r="M151" s="39">
+        <f>IF(A151="","",IF(E151="Interno","Interno",IF(K151=0,"Sem horas",IF(L151&gt;N(F151),"Consome mais do que paga",IF(AND(N(G151)&gt;0,K151/G151&gt;1),"Estourou as horas",IF(AND(N(F151)&gt;0,(F151-L151)/F151&lt;0.2),"Margem baixa",IF(AND(N(G151)&gt;0,K151/G151&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="41" t="n"/>
@@ -8672,6 +10466,18 @@
       <c r="G152" s="46" t="n"/>
       <c r="H152" s="47" t="n"/>
       <c r="I152" s="42" t="n"/>
+      <c r="K152" s="39">
+        <f>IF(A152="","",N(H152)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A152))</f>
+        <v/>
+      </c>
+      <c r="L152" s="39">
+        <f>IF(A152="","",N(H152)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A152))</f>
+        <v/>
+      </c>
+      <c r="M152" s="39">
+        <f>IF(A152="","",IF(E152="Interno","Interno",IF(K152=0,"Sem horas",IF(L152&gt;N(F152),"Consome mais do que paga",IF(AND(N(G152)&gt;0,K152/G152&gt;1),"Estourou as horas",IF(AND(N(F152)&gt;0,(F152-L152)/F152&lt;0.2),"Margem baixa",IF(AND(N(G152)&gt;0,K152/G152&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="41" t="n"/>
@@ -8683,6 +10489,18 @@
       <c r="G153" s="46" t="n"/>
       <c r="H153" s="47" t="n"/>
       <c r="I153" s="42" t="n"/>
+      <c r="K153" s="39">
+        <f>IF(A153="","",N(H153)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A153))</f>
+        <v/>
+      </c>
+      <c r="L153" s="39">
+        <f>IF(A153="","",N(H153)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A153))</f>
+        <v/>
+      </c>
+      <c r="M153" s="39">
+        <f>IF(A153="","",IF(E153="Interno","Interno",IF(K153=0,"Sem horas",IF(L153&gt;N(F153),"Consome mais do que paga",IF(AND(N(G153)&gt;0,K153/G153&gt;1),"Estourou as horas",IF(AND(N(F153)&gt;0,(F153-L153)/F153&lt;0.2),"Margem baixa",IF(AND(N(G153)&gt;0,K153/G153&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="41" t="n"/>
@@ -8694,6 +10512,18 @@
       <c r="G154" s="46" t="n"/>
       <c r="H154" s="47" t="n"/>
       <c r="I154" s="42" t="n"/>
+      <c r="K154" s="39">
+        <f>IF(A154="","",N(H154)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A154))</f>
+        <v/>
+      </c>
+      <c r="L154" s="39">
+        <f>IF(A154="","",N(H154)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A154))</f>
+        <v/>
+      </c>
+      <c r="M154" s="39">
+        <f>IF(A154="","",IF(E154="Interno","Interno",IF(K154=0,"Sem horas",IF(L154&gt;N(F154),"Consome mais do que paga",IF(AND(N(G154)&gt;0,K154/G154&gt;1),"Estourou as horas",IF(AND(N(F154)&gt;0,(F154-L154)/F154&lt;0.2),"Margem baixa",IF(AND(N(G154)&gt;0,K154/G154&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="41" t="n"/>
@@ -8705,6 +10535,18 @@
       <c r="G155" s="46" t="n"/>
       <c r="H155" s="47" t="n"/>
       <c r="I155" s="42" t="n"/>
+      <c r="K155" s="39">
+        <f>IF(A155="","",N(H155)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A155))</f>
+        <v/>
+      </c>
+      <c r="L155" s="39">
+        <f>IF(A155="","",N(H155)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A155))</f>
+        <v/>
+      </c>
+      <c r="M155" s="39">
+        <f>IF(A155="","",IF(E155="Interno","Interno",IF(K155=0,"Sem horas",IF(L155&gt;N(F155),"Consome mais do que paga",IF(AND(N(G155)&gt;0,K155/G155&gt;1),"Estourou as horas",IF(AND(N(F155)&gt;0,(F155-L155)/F155&lt;0.2),"Margem baixa",IF(AND(N(G155)&gt;0,K155/G155&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="41" t="n"/>
@@ -8716,6 +10558,18 @@
       <c r="G156" s="46" t="n"/>
       <c r="H156" s="47" t="n"/>
       <c r="I156" s="42" t="n"/>
+      <c r="K156" s="39">
+        <f>IF(A156="","",N(H156)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A156))</f>
+        <v/>
+      </c>
+      <c r="L156" s="39">
+        <f>IF(A156="","",N(H156)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A156))</f>
+        <v/>
+      </c>
+      <c r="M156" s="39">
+        <f>IF(A156="","",IF(E156="Interno","Interno",IF(K156=0,"Sem horas",IF(L156&gt;N(F156),"Consome mais do que paga",IF(AND(N(G156)&gt;0,K156/G156&gt;1),"Estourou as horas",IF(AND(N(F156)&gt;0,(F156-L156)/F156&lt;0.2),"Margem baixa",IF(AND(N(G156)&gt;0,K156/G156&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="41" t="n"/>
@@ -8727,6 +10581,18 @@
       <c r="G157" s="46" t="n"/>
       <c r="H157" s="47" t="n"/>
       <c r="I157" s="42" t="n"/>
+      <c r="K157" s="39">
+        <f>IF(A157="","",N(H157)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A157))</f>
+        <v/>
+      </c>
+      <c r="L157" s="39">
+        <f>IF(A157="","",N(H157)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A157))</f>
+        <v/>
+      </c>
+      <c r="M157" s="39">
+        <f>IF(A157="","",IF(E157="Interno","Interno",IF(K157=0,"Sem horas",IF(L157&gt;N(F157),"Consome mais do que paga",IF(AND(N(G157)&gt;0,K157/G157&gt;1),"Estourou as horas",IF(AND(N(F157)&gt;0,(F157-L157)/F157&lt;0.2),"Margem baixa",IF(AND(N(G157)&gt;0,K157/G157&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="41" t="n"/>
@@ -8738,6 +10604,18 @@
       <c r="G158" s="46" t="n"/>
       <c r="H158" s="47" t="n"/>
       <c r="I158" s="42" t="n"/>
+      <c r="K158" s="39">
+        <f>IF(A158="","",N(H158)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A158))</f>
+        <v/>
+      </c>
+      <c r="L158" s="39">
+        <f>IF(A158="","",N(H158)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A158))</f>
+        <v/>
+      </c>
+      <c r="M158" s="39">
+        <f>IF(A158="","",IF(E158="Interno","Interno",IF(K158=0,"Sem horas",IF(L158&gt;N(F158),"Consome mais do que paga",IF(AND(N(G158)&gt;0,K158/G158&gt;1),"Estourou as horas",IF(AND(N(F158)&gt;0,(F158-L158)/F158&lt;0.2),"Margem baixa",IF(AND(N(G158)&gt;0,K158/G158&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="41" t="n"/>
@@ -8749,6 +10627,18 @@
       <c r="G159" s="46" t="n"/>
       <c r="H159" s="47" t="n"/>
       <c r="I159" s="42" t="n"/>
+      <c r="K159" s="39">
+        <f>IF(A159="","",N(H159)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A159))</f>
+        <v/>
+      </c>
+      <c r="L159" s="39">
+        <f>IF(A159="","",N(H159)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A159))</f>
+        <v/>
+      </c>
+      <c r="M159" s="39">
+        <f>IF(A159="","",IF(E159="Interno","Interno",IF(K159=0,"Sem horas",IF(L159&gt;N(F159),"Consome mais do que paga",IF(AND(N(G159)&gt;0,K159/G159&gt;1),"Estourou as horas",IF(AND(N(F159)&gt;0,(F159-L159)/F159&lt;0.2),"Margem baixa",IF(AND(N(G159)&gt;0,K159/G159&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="41" t="n"/>
@@ -8760,6 +10650,18 @@
       <c r="G160" s="46" t="n"/>
       <c r="H160" s="47" t="n"/>
       <c r="I160" s="42" t="n"/>
+      <c r="K160" s="39">
+        <f>IF(A160="","",N(H160)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A160))</f>
+        <v/>
+      </c>
+      <c r="L160" s="39">
+        <f>IF(A160="","",N(H160)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A160))</f>
+        <v/>
+      </c>
+      <c r="M160" s="39">
+        <f>IF(A160="","",IF(E160="Interno","Interno",IF(K160=0,"Sem horas",IF(L160&gt;N(F160),"Consome mais do que paga",IF(AND(N(G160)&gt;0,K160/G160&gt;1),"Estourou as horas",IF(AND(N(F160)&gt;0,(F160-L160)/F160&lt;0.2),"Margem baixa",IF(AND(N(G160)&gt;0,K160/G160&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="41" t="n"/>
@@ -8771,6 +10673,18 @@
       <c r="G161" s="46" t="n"/>
       <c r="H161" s="47" t="n"/>
       <c r="I161" s="42" t="n"/>
+      <c r="K161" s="39">
+        <f>IF(A161="","",N(H161)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A161))</f>
+        <v/>
+      </c>
+      <c r="L161" s="39">
+        <f>IF(A161="","",N(H161)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A161))</f>
+        <v/>
+      </c>
+      <c r="M161" s="39">
+        <f>IF(A161="","",IF(E161="Interno","Interno",IF(K161=0,"Sem horas",IF(L161&gt;N(F161),"Consome mais do que paga",IF(AND(N(G161)&gt;0,K161/G161&gt;1),"Estourou as horas",IF(AND(N(F161)&gt;0,(F161-L161)/F161&lt;0.2),"Margem baixa",IF(AND(N(G161)&gt;0,K161/G161&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="41" t="n"/>
@@ -8782,6 +10696,18 @@
       <c r="G162" s="46" t="n"/>
       <c r="H162" s="47" t="n"/>
       <c r="I162" s="42" t="n"/>
+      <c r="K162" s="39">
+        <f>IF(A162="","",N(H162)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A162))</f>
+        <v/>
+      </c>
+      <c r="L162" s="39">
+        <f>IF(A162="","",N(H162)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A162))</f>
+        <v/>
+      </c>
+      <c r="M162" s="39">
+        <f>IF(A162="","",IF(E162="Interno","Interno",IF(K162=0,"Sem horas",IF(L162&gt;N(F162),"Consome mais do que paga",IF(AND(N(G162)&gt;0,K162/G162&gt;1),"Estourou as horas",IF(AND(N(F162)&gt;0,(F162-L162)/F162&lt;0.2),"Margem baixa",IF(AND(N(G162)&gt;0,K162/G162&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="41" t="n"/>
@@ -8793,6 +10719,18 @@
       <c r="G163" s="46" t="n"/>
       <c r="H163" s="47" t="n"/>
       <c r="I163" s="42" t="n"/>
+      <c r="K163" s="39">
+        <f>IF(A163="","",N(H163)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A163))</f>
+        <v/>
+      </c>
+      <c r="L163" s="39">
+        <f>IF(A163="","",N(H163)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A163))</f>
+        <v/>
+      </c>
+      <c r="M163" s="39">
+        <f>IF(A163="","",IF(E163="Interno","Interno",IF(K163=0,"Sem horas",IF(L163&gt;N(F163),"Consome mais do que paga",IF(AND(N(G163)&gt;0,K163/G163&gt;1),"Estourou as horas",IF(AND(N(F163)&gt;0,(F163-L163)/F163&lt;0.2),"Margem baixa",IF(AND(N(G163)&gt;0,K163/G163&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="41" t="n"/>
@@ -8804,6 +10742,18 @@
       <c r="G164" s="46" t="n"/>
       <c r="H164" s="47" t="n"/>
       <c r="I164" s="42" t="n"/>
+      <c r="K164" s="39">
+        <f>IF(A164="","",N(H164)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A164))</f>
+        <v/>
+      </c>
+      <c r="L164" s="39">
+        <f>IF(A164="","",N(H164)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A164))</f>
+        <v/>
+      </c>
+      <c r="M164" s="39">
+        <f>IF(A164="","",IF(E164="Interno","Interno",IF(K164=0,"Sem horas",IF(L164&gt;N(F164),"Consome mais do que paga",IF(AND(N(G164)&gt;0,K164/G164&gt;1),"Estourou as horas",IF(AND(N(F164)&gt;0,(F164-L164)/F164&lt;0.2),"Margem baixa",IF(AND(N(G164)&gt;0,K164/G164&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="41" t="n"/>
@@ -8815,6 +10765,18 @@
       <c r="G165" s="46" t="n"/>
       <c r="H165" s="47" t="n"/>
       <c r="I165" s="42" t="n"/>
+      <c r="K165" s="39">
+        <f>IF(A165="","",N(H165)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A165))</f>
+        <v/>
+      </c>
+      <c r="L165" s="39">
+        <f>IF(A165="","",N(H165)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A165))</f>
+        <v/>
+      </c>
+      <c r="M165" s="39">
+        <f>IF(A165="","",IF(E165="Interno","Interno",IF(K165=0,"Sem horas",IF(L165&gt;N(F165),"Consome mais do que paga",IF(AND(N(G165)&gt;0,K165/G165&gt;1),"Estourou as horas",IF(AND(N(F165)&gt;0,(F165-L165)/F165&lt;0.2),"Margem baixa",IF(AND(N(G165)&gt;0,K165/G165&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="41" t="n"/>
@@ -8826,6 +10788,18 @@
       <c r="G166" s="46" t="n"/>
       <c r="H166" s="47" t="n"/>
       <c r="I166" s="42" t="n"/>
+      <c r="K166" s="39">
+        <f>IF(A166="","",N(H166)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A166))</f>
+        <v/>
+      </c>
+      <c r="L166" s="39">
+        <f>IF(A166="","",N(H166)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A166))</f>
+        <v/>
+      </c>
+      <c r="M166" s="39">
+        <f>IF(A166="","",IF(E166="Interno","Interno",IF(K166=0,"Sem horas",IF(L166&gt;N(F166),"Consome mais do que paga",IF(AND(N(G166)&gt;0,K166/G166&gt;1),"Estourou as horas",IF(AND(N(F166)&gt;0,(F166-L166)/F166&lt;0.2),"Margem baixa",IF(AND(N(G166)&gt;0,K166/G166&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="41" t="n"/>
@@ -8837,6 +10811,18 @@
       <c r="G167" s="46" t="n"/>
       <c r="H167" s="47" t="n"/>
       <c r="I167" s="42" t="n"/>
+      <c r="K167" s="39">
+        <f>IF(A167="","",N(H167)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A167))</f>
+        <v/>
+      </c>
+      <c r="L167" s="39">
+        <f>IF(A167="","",N(H167)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A167))</f>
+        <v/>
+      </c>
+      <c r="M167" s="39">
+        <f>IF(A167="","",IF(E167="Interno","Interno",IF(K167=0,"Sem horas",IF(L167&gt;N(F167),"Consome mais do que paga",IF(AND(N(G167)&gt;0,K167/G167&gt;1),"Estourou as horas",IF(AND(N(F167)&gt;0,(F167-L167)/F167&lt;0.2),"Margem baixa",IF(AND(N(G167)&gt;0,K167/G167&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="41" t="n"/>
@@ -8848,6 +10834,18 @@
       <c r="G168" s="46" t="n"/>
       <c r="H168" s="47" t="n"/>
       <c r="I168" s="42" t="n"/>
+      <c r="K168" s="39">
+        <f>IF(A168="","",N(H168)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A168))</f>
+        <v/>
+      </c>
+      <c r="L168" s="39">
+        <f>IF(A168="","",N(H168)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A168))</f>
+        <v/>
+      </c>
+      <c r="M168" s="39">
+        <f>IF(A168="","",IF(E168="Interno","Interno",IF(K168=0,"Sem horas",IF(L168&gt;N(F168),"Consome mais do que paga",IF(AND(N(G168)&gt;0,K168/G168&gt;1),"Estourou as horas",IF(AND(N(F168)&gt;0,(F168-L168)/F168&lt;0.2),"Margem baixa",IF(AND(N(G168)&gt;0,K168/G168&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="41" t="n"/>
@@ -8859,6 +10857,18 @@
       <c r="G169" s="46" t="n"/>
       <c r="H169" s="47" t="n"/>
       <c r="I169" s="42" t="n"/>
+      <c r="K169" s="39">
+        <f>IF(A169="","",N(H169)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A169))</f>
+        <v/>
+      </c>
+      <c r="L169" s="39">
+        <f>IF(A169="","",N(H169)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A169))</f>
+        <v/>
+      </c>
+      <c r="M169" s="39">
+        <f>IF(A169="","",IF(E169="Interno","Interno",IF(K169=0,"Sem horas",IF(L169&gt;N(F169),"Consome mais do que paga",IF(AND(N(G169)&gt;0,K169/G169&gt;1),"Estourou as horas",IF(AND(N(F169)&gt;0,(F169-L169)/F169&lt;0.2),"Margem baixa",IF(AND(N(G169)&gt;0,K169/G169&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="41" t="n"/>
@@ -8870,6 +10880,18 @@
       <c r="G170" s="46" t="n"/>
       <c r="H170" s="47" t="n"/>
       <c r="I170" s="42" t="n"/>
+      <c r="K170" s="39">
+        <f>IF(A170="","",N(H170)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A170))</f>
+        <v/>
+      </c>
+      <c r="L170" s="39">
+        <f>IF(A170="","",N(H170)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A170))</f>
+        <v/>
+      </c>
+      <c r="M170" s="39">
+        <f>IF(A170="","",IF(E170="Interno","Interno",IF(K170=0,"Sem horas",IF(L170&gt;N(F170),"Consome mais do que paga",IF(AND(N(G170)&gt;0,K170/G170&gt;1),"Estourou as horas",IF(AND(N(F170)&gt;0,(F170-L170)/F170&lt;0.2),"Margem baixa",IF(AND(N(G170)&gt;0,K170/G170&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="41" t="n"/>
@@ -8881,6 +10903,18 @@
       <c r="G171" s="46" t="n"/>
       <c r="H171" s="47" t="n"/>
       <c r="I171" s="42" t="n"/>
+      <c r="K171" s="39">
+        <f>IF(A171="","",N(H171)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A171))</f>
+        <v/>
+      </c>
+      <c r="L171" s="39">
+        <f>IF(A171="","",N(H171)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A171))</f>
+        <v/>
+      </c>
+      <c r="M171" s="39">
+        <f>IF(A171="","",IF(E171="Interno","Interno",IF(K171=0,"Sem horas",IF(L171&gt;N(F171),"Consome mais do que paga",IF(AND(N(G171)&gt;0,K171/G171&gt;1),"Estourou as horas",IF(AND(N(F171)&gt;0,(F171-L171)/F171&lt;0.2),"Margem baixa",IF(AND(N(G171)&gt;0,K171/G171&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="41" t="n"/>
@@ -8892,6 +10926,18 @@
       <c r="G172" s="46" t="n"/>
       <c r="H172" s="47" t="n"/>
       <c r="I172" s="42" t="n"/>
+      <c r="K172" s="39">
+        <f>IF(A172="","",N(H172)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A172))</f>
+        <v/>
+      </c>
+      <c r="L172" s="39">
+        <f>IF(A172="","",N(H172)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A172))</f>
+        <v/>
+      </c>
+      <c r="M172" s="39">
+        <f>IF(A172="","",IF(E172="Interno","Interno",IF(K172=0,"Sem horas",IF(L172&gt;N(F172),"Consome mais do que paga",IF(AND(N(G172)&gt;0,K172/G172&gt;1),"Estourou as horas",IF(AND(N(F172)&gt;0,(F172-L172)/F172&lt;0.2),"Margem baixa",IF(AND(N(G172)&gt;0,K172/G172&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="41" t="n"/>
@@ -8903,6 +10949,18 @@
       <c r="G173" s="46" t="n"/>
       <c r="H173" s="47" t="n"/>
       <c r="I173" s="42" t="n"/>
+      <c r="K173" s="39">
+        <f>IF(A173="","",N(H173)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A173))</f>
+        <v/>
+      </c>
+      <c r="L173" s="39">
+        <f>IF(A173="","",N(H173)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A173))</f>
+        <v/>
+      </c>
+      <c r="M173" s="39">
+        <f>IF(A173="","",IF(E173="Interno","Interno",IF(K173=0,"Sem horas",IF(L173&gt;N(F173),"Consome mais do que paga",IF(AND(N(G173)&gt;0,K173/G173&gt;1),"Estourou as horas",IF(AND(N(F173)&gt;0,(F173-L173)/F173&lt;0.2),"Margem baixa",IF(AND(N(G173)&gt;0,K173/G173&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="41" t="n"/>
@@ -8914,6 +10972,18 @@
       <c r="G174" s="46" t="n"/>
       <c r="H174" s="47" t="n"/>
       <c r="I174" s="42" t="n"/>
+      <c r="K174" s="39">
+        <f>IF(A174="","",N(H174)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A174))</f>
+        <v/>
+      </c>
+      <c r="L174" s="39">
+        <f>IF(A174="","",N(H174)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A174))</f>
+        <v/>
+      </c>
+      <c r="M174" s="39">
+        <f>IF(A174="","",IF(E174="Interno","Interno",IF(K174=0,"Sem horas",IF(L174&gt;N(F174),"Consome mais do que paga",IF(AND(N(G174)&gt;0,K174/G174&gt;1),"Estourou as horas",IF(AND(N(F174)&gt;0,(F174-L174)/F174&lt;0.2),"Margem baixa",IF(AND(N(G174)&gt;0,K174/G174&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="41" t="n"/>
@@ -8925,6 +10995,18 @@
       <c r="G175" s="46" t="n"/>
       <c r="H175" s="47" t="n"/>
       <c r="I175" s="42" t="n"/>
+      <c r="K175" s="39">
+        <f>IF(A175="","",N(H175)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A175))</f>
+        <v/>
+      </c>
+      <c r="L175" s="39">
+        <f>IF(A175="","",N(H175)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A175))</f>
+        <v/>
+      </c>
+      <c r="M175" s="39">
+        <f>IF(A175="","",IF(E175="Interno","Interno",IF(K175=0,"Sem horas",IF(L175&gt;N(F175),"Consome mais do que paga",IF(AND(N(G175)&gt;0,K175/G175&gt;1),"Estourou as horas",IF(AND(N(F175)&gt;0,(F175-L175)/F175&lt;0.2),"Margem baixa",IF(AND(N(G175)&gt;0,K175/G175&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="41" t="n"/>
@@ -8936,6 +11018,18 @@
       <c r="G176" s="46" t="n"/>
       <c r="H176" s="47" t="n"/>
       <c r="I176" s="42" t="n"/>
+      <c r="K176" s="39">
+        <f>IF(A176="","",N(H176)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A176))</f>
+        <v/>
+      </c>
+      <c r="L176" s="39">
+        <f>IF(A176="","",N(H176)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A176))</f>
+        <v/>
+      </c>
+      <c r="M176" s="39">
+        <f>IF(A176="","",IF(E176="Interno","Interno",IF(K176=0,"Sem horas",IF(L176&gt;N(F176),"Consome mais do que paga",IF(AND(N(G176)&gt;0,K176/G176&gt;1),"Estourou as horas",IF(AND(N(F176)&gt;0,(F176-L176)/F176&lt;0.2),"Margem baixa",IF(AND(N(G176)&gt;0,K176/G176&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="41" t="n"/>
@@ -8947,6 +11041,18 @@
       <c r="G177" s="46" t="n"/>
       <c r="H177" s="47" t="n"/>
       <c r="I177" s="42" t="n"/>
+      <c r="K177" s="39">
+        <f>IF(A177="","",N(H177)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A177))</f>
+        <v/>
+      </c>
+      <c r="L177" s="39">
+        <f>IF(A177="","",N(H177)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A177))</f>
+        <v/>
+      </c>
+      <c r="M177" s="39">
+        <f>IF(A177="","",IF(E177="Interno","Interno",IF(K177=0,"Sem horas",IF(L177&gt;N(F177),"Consome mais do que paga",IF(AND(N(G177)&gt;0,K177/G177&gt;1),"Estourou as horas",IF(AND(N(F177)&gt;0,(F177-L177)/F177&lt;0.2),"Margem baixa",IF(AND(N(G177)&gt;0,K177/G177&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="41" t="n"/>
@@ -8958,6 +11064,18 @@
       <c r="G178" s="46" t="n"/>
       <c r="H178" s="47" t="n"/>
       <c r="I178" s="42" t="n"/>
+      <c r="K178" s="39">
+        <f>IF(A178="","",N(H178)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A178))</f>
+        <v/>
+      </c>
+      <c r="L178" s="39">
+        <f>IF(A178="","",N(H178)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A178))</f>
+        <v/>
+      </c>
+      <c r="M178" s="39">
+        <f>IF(A178="","",IF(E178="Interno","Interno",IF(K178=0,"Sem horas",IF(L178&gt;N(F178),"Consome mais do que paga",IF(AND(N(G178)&gt;0,K178/G178&gt;1),"Estourou as horas",IF(AND(N(F178)&gt;0,(F178-L178)/F178&lt;0.2),"Margem baixa",IF(AND(N(G178)&gt;0,K178/G178&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="41" t="n"/>
@@ -8969,6 +11087,18 @@
       <c r="G179" s="46" t="n"/>
       <c r="H179" s="47" t="n"/>
       <c r="I179" s="42" t="n"/>
+      <c r="K179" s="39">
+        <f>IF(A179="","",N(H179)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A179))</f>
+        <v/>
+      </c>
+      <c r="L179" s="39">
+        <f>IF(A179="","",N(H179)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A179))</f>
+        <v/>
+      </c>
+      <c r="M179" s="39">
+        <f>IF(A179="","",IF(E179="Interno","Interno",IF(K179=0,"Sem horas",IF(L179&gt;N(F179),"Consome mais do que paga",IF(AND(N(G179)&gt;0,K179/G179&gt;1),"Estourou as horas",IF(AND(N(F179)&gt;0,(F179-L179)/F179&lt;0.2),"Margem baixa",IF(AND(N(G179)&gt;0,K179/G179&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="41" t="n"/>
@@ -8980,6 +11110,18 @@
       <c r="G180" s="46" t="n"/>
       <c r="H180" s="47" t="n"/>
       <c r="I180" s="42" t="n"/>
+      <c r="K180" s="39">
+        <f>IF(A180="","",N(H180)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A180))</f>
+        <v/>
+      </c>
+      <c r="L180" s="39">
+        <f>IF(A180="","",N(H180)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A180))</f>
+        <v/>
+      </c>
+      <c r="M180" s="39">
+        <f>IF(A180="","",IF(E180="Interno","Interno",IF(K180=0,"Sem horas",IF(L180&gt;N(F180),"Consome mais do que paga",IF(AND(N(G180)&gt;0,K180/G180&gt;1),"Estourou as horas",IF(AND(N(F180)&gt;0,(F180-L180)/F180&lt;0.2),"Margem baixa",IF(AND(N(G180)&gt;0,K180/G180&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="41" t="n"/>
@@ -8991,6 +11133,18 @@
       <c r="G181" s="46" t="n"/>
       <c r="H181" s="47" t="n"/>
       <c r="I181" s="42" t="n"/>
+      <c r="K181" s="39">
+        <f>IF(A181="","",N(H181)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A181))</f>
+        <v/>
+      </c>
+      <c r="L181" s="39">
+        <f>IF(A181="","",N(H181)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A181))</f>
+        <v/>
+      </c>
+      <c r="M181" s="39">
+        <f>IF(A181="","",IF(E181="Interno","Interno",IF(K181=0,"Sem horas",IF(L181&gt;N(F181),"Consome mais do que paga",IF(AND(N(G181)&gt;0,K181/G181&gt;1),"Estourou as horas",IF(AND(N(F181)&gt;0,(F181-L181)/F181&lt;0.2),"Margem baixa",IF(AND(N(G181)&gt;0,K181/G181&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="41" t="n"/>
@@ -9002,6 +11156,18 @@
       <c r="G182" s="46" t="n"/>
       <c r="H182" s="47" t="n"/>
       <c r="I182" s="42" t="n"/>
+      <c r="K182" s="39">
+        <f>IF(A182="","",N(H182)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A182))</f>
+        <v/>
+      </c>
+      <c r="L182" s="39">
+        <f>IF(A182="","",N(H182)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A182))</f>
+        <v/>
+      </c>
+      <c r="M182" s="39">
+        <f>IF(A182="","",IF(E182="Interno","Interno",IF(K182=0,"Sem horas",IF(L182&gt;N(F182),"Consome mais do que paga",IF(AND(N(G182)&gt;0,K182/G182&gt;1),"Estourou as horas",IF(AND(N(F182)&gt;0,(F182-L182)/F182&lt;0.2),"Margem baixa",IF(AND(N(G182)&gt;0,K182/G182&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="41" t="n"/>
@@ -9013,6 +11179,18 @@
       <c r="G183" s="46" t="n"/>
       <c r="H183" s="47" t="n"/>
       <c r="I183" s="42" t="n"/>
+      <c r="K183" s="39">
+        <f>IF(A183="","",N(H183)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A183))</f>
+        <v/>
+      </c>
+      <c r="L183" s="39">
+        <f>IF(A183="","",N(H183)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A183))</f>
+        <v/>
+      </c>
+      <c r="M183" s="39">
+        <f>IF(A183="","",IF(E183="Interno","Interno",IF(K183=0,"Sem horas",IF(L183&gt;N(F183),"Consome mais do que paga",IF(AND(N(G183)&gt;0,K183/G183&gt;1),"Estourou as horas",IF(AND(N(F183)&gt;0,(F183-L183)/F183&lt;0.2),"Margem baixa",IF(AND(N(G183)&gt;0,K183/G183&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="41" t="n"/>
@@ -9024,6 +11202,18 @@
       <c r="G184" s="46" t="n"/>
       <c r="H184" s="47" t="n"/>
       <c r="I184" s="42" t="n"/>
+      <c r="K184" s="39">
+        <f>IF(A184="","",N(H184)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A184))</f>
+        <v/>
+      </c>
+      <c r="L184" s="39">
+        <f>IF(A184="","",N(H184)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A184))</f>
+        <v/>
+      </c>
+      <c r="M184" s="39">
+        <f>IF(A184="","",IF(E184="Interno","Interno",IF(K184=0,"Sem horas",IF(L184&gt;N(F184),"Consome mais do que paga",IF(AND(N(G184)&gt;0,K184/G184&gt;1),"Estourou as horas",IF(AND(N(F184)&gt;0,(F184-L184)/F184&lt;0.2),"Margem baixa",IF(AND(N(G184)&gt;0,K184/G184&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="41" t="n"/>
@@ -9035,6 +11225,18 @@
       <c r="G185" s="46" t="n"/>
       <c r="H185" s="47" t="n"/>
       <c r="I185" s="42" t="n"/>
+      <c r="K185" s="39">
+        <f>IF(A185="","",N(H185)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A185))</f>
+        <v/>
+      </c>
+      <c r="L185" s="39">
+        <f>IF(A185="","",N(H185)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A185))</f>
+        <v/>
+      </c>
+      <c r="M185" s="39">
+        <f>IF(A185="","",IF(E185="Interno","Interno",IF(K185=0,"Sem horas",IF(L185&gt;N(F185),"Consome mais do que paga",IF(AND(N(G185)&gt;0,K185/G185&gt;1),"Estourou as horas",IF(AND(N(F185)&gt;0,(F185-L185)/F185&lt;0.2),"Margem baixa",IF(AND(N(G185)&gt;0,K185/G185&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="41" t="n"/>
@@ -9046,6 +11248,18 @@
       <c r="G186" s="46" t="n"/>
       <c r="H186" s="47" t="n"/>
       <c r="I186" s="42" t="n"/>
+      <c r="K186" s="39">
+        <f>IF(A186="","",N(H186)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A186))</f>
+        <v/>
+      </c>
+      <c r="L186" s="39">
+        <f>IF(A186="","",N(H186)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A186))</f>
+        <v/>
+      </c>
+      <c r="M186" s="39">
+        <f>IF(A186="","",IF(E186="Interno","Interno",IF(K186=0,"Sem horas",IF(L186&gt;N(F186),"Consome mais do que paga",IF(AND(N(G186)&gt;0,K186/G186&gt;1),"Estourou as horas",IF(AND(N(F186)&gt;0,(F186-L186)/F186&lt;0.2),"Margem baixa",IF(AND(N(G186)&gt;0,K186/G186&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="41" t="n"/>
@@ -9057,6 +11271,18 @@
       <c r="G187" s="46" t="n"/>
       <c r="H187" s="47" t="n"/>
       <c r="I187" s="42" t="n"/>
+      <c r="K187" s="39">
+        <f>IF(A187="","",N(H187)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A187))</f>
+        <v/>
+      </c>
+      <c r="L187" s="39">
+        <f>IF(A187="","",N(H187)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A187))</f>
+        <v/>
+      </c>
+      <c r="M187" s="39">
+        <f>IF(A187="","",IF(E187="Interno","Interno",IF(K187=0,"Sem horas",IF(L187&gt;N(F187),"Consome mais do que paga",IF(AND(N(G187)&gt;0,K187/G187&gt;1),"Estourou as horas",IF(AND(N(F187)&gt;0,(F187-L187)/F187&lt;0.2),"Margem baixa",IF(AND(N(G187)&gt;0,K187/G187&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="41" t="n"/>
@@ -9068,6 +11294,18 @@
       <c r="G188" s="46" t="n"/>
       <c r="H188" s="47" t="n"/>
       <c r="I188" s="42" t="n"/>
+      <c r="K188" s="39">
+        <f>IF(A188="","",N(H188)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A188))</f>
+        <v/>
+      </c>
+      <c r="L188" s="39">
+        <f>IF(A188="","",N(H188)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A188))</f>
+        <v/>
+      </c>
+      <c r="M188" s="39">
+        <f>IF(A188="","",IF(E188="Interno","Interno",IF(K188=0,"Sem horas",IF(L188&gt;N(F188),"Consome mais do que paga",IF(AND(N(G188)&gt;0,K188/G188&gt;1),"Estourou as horas",IF(AND(N(F188)&gt;0,(F188-L188)/F188&lt;0.2),"Margem baixa",IF(AND(N(G188)&gt;0,K188/G188&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="41" t="n"/>
@@ -9079,6 +11317,18 @@
       <c r="G189" s="46" t="n"/>
       <c r="H189" s="47" t="n"/>
       <c r="I189" s="42" t="n"/>
+      <c r="K189" s="39">
+        <f>IF(A189="","",N(H189)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A189))</f>
+        <v/>
+      </c>
+      <c r="L189" s="39">
+        <f>IF(A189="","",N(H189)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A189))</f>
+        <v/>
+      </c>
+      <c r="M189" s="39">
+        <f>IF(A189="","",IF(E189="Interno","Interno",IF(K189=0,"Sem horas",IF(L189&gt;N(F189),"Consome mais do que paga",IF(AND(N(G189)&gt;0,K189/G189&gt;1),"Estourou as horas",IF(AND(N(F189)&gt;0,(F189-L189)/F189&lt;0.2),"Margem baixa",IF(AND(N(G189)&gt;0,K189/G189&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="41" t="n"/>
@@ -9090,6 +11340,18 @@
       <c r="G190" s="46" t="n"/>
       <c r="H190" s="47" t="n"/>
       <c r="I190" s="42" t="n"/>
+      <c r="K190" s="39">
+        <f>IF(A190="","",N(H190)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A190))</f>
+        <v/>
+      </c>
+      <c r="L190" s="39">
+        <f>IF(A190="","",N(H190)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A190))</f>
+        <v/>
+      </c>
+      <c r="M190" s="39">
+        <f>IF(A190="","",IF(E190="Interno","Interno",IF(K190=0,"Sem horas",IF(L190&gt;N(F190),"Consome mais do que paga",IF(AND(N(G190)&gt;0,K190/G190&gt;1),"Estourou as horas",IF(AND(N(F190)&gt;0,(F190-L190)/F190&lt;0.2),"Margem baixa",IF(AND(N(G190)&gt;0,K190/G190&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="41" t="n"/>
@@ -9101,6 +11363,18 @@
       <c r="G191" s="46" t="n"/>
       <c r="H191" s="47" t="n"/>
       <c r="I191" s="42" t="n"/>
+      <c r="K191" s="39">
+        <f>IF(A191="","",N(H191)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A191))</f>
+        <v/>
+      </c>
+      <c r="L191" s="39">
+        <f>IF(A191="","",N(H191)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A191))</f>
+        <v/>
+      </c>
+      <c r="M191" s="39">
+        <f>IF(A191="","",IF(E191="Interno","Interno",IF(K191=0,"Sem horas",IF(L191&gt;N(F191),"Consome mais do que paga",IF(AND(N(G191)&gt;0,K191/G191&gt;1),"Estourou as horas",IF(AND(N(F191)&gt;0,(F191-L191)/F191&lt;0.2),"Margem baixa",IF(AND(N(G191)&gt;0,K191/G191&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="41" t="n"/>
@@ -9112,6 +11386,18 @@
       <c r="G192" s="46" t="n"/>
       <c r="H192" s="47" t="n"/>
       <c r="I192" s="42" t="n"/>
+      <c r="K192" s="39">
+        <f>IF(A192="","",N(H192)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A192))</f>
+        <v/>
+      </c>
+      <c r="L192" s="39">
+        <f>IF(A192="","",N(H192)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A192))</f>
+        <v/>
+      </c>
+      <c r="M192" s="39">
+        <f>IF(A192="","",IF(E192="Interno","Interno",IF(K192=0,"Sem horas",IF(L192&gt;N(F192),"Consome mais do que paga",IF(AND(N(G192)&gt;0,K192/G192&gt;1),"Estourou as horas",IF(AND(N(F192)&gt;0,(F192-L192)/F192&lt;0.2),"Margem baixa",IF(AND(N(G192)&gt;0,K192/G192&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="41" t="n"/>
@@ -9123,6 +11409,18 @@
       <c r="G193" s="46" t="n"/>
       <c r="H193" s="47" t="n"/>
       <c r="I193" s="42" t="n"/>
+      <c r="K193" s="39">
+        <f>IF(A193="","",N(H193)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A193))</f>
+        <v/>
+      </c>
+      <c r="L193" s="39">
+        <f>IF(A193="","",N(H193)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A193))</f>
+        <v/>
+      </c>
+      <c r="M193" s="39">
+        <f>IF(A193="","",IF(E193="Interno","Interno",IF(K193=0,"Sem horas",IF(L193&gt;N(F193),"Consome mais do que paga",IF(AND(N(G193)&gt;0,K193/G193&gt;1),"Estourou as horas",IF(AND(N(F193)&gt;0,(F193-L193)/F193&lt;0.2),"Margem baixa",IF(AND(N(G193)&gt;0,K193/G193&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="41" t="n"/>
@@ -9134,6 +11432,18 @@
       <c r="G194" s="46" t="n"/>
       <c r="H194" s="47" t="n"/>
       <c r="I194" s="42" t="n"/>
+      <c r="K194" s="39">
+        <f>IF(A194="","",N(H194)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A194))</f>
+        <v/>
+      </c>
+      <c r="L194" s="39">
+        <f>IF(A194="","",N(H194)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A194))</f>
+        <v/>
+      </c>
+      <c r="M194" s="39">
+        <f>IF(A194="","",IF(E194="Interno","Interno",IF(K194=0,"Sem horas",IF(L194&gt;N(F194),"Consome mais do que paga",IF(AND(N(G194)&gt;0,K194/G194&gt;1),"Estourou as horas",IF(AND(N(F194)&gt;0,(F194-L194)/F194&lt;0.2),"Margem baixa",IF(AND(N(G194)&gt;0,K194/G194&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="41" t="n"/>
@@ -9145,6 +11455,18 @@
       <c r="G195" s="46" t="n"/>
       <c r="H195" s="47" t="n"/>
       <c r="I195" s="42" t="n"/>
+      <c r="K195" s="39">
+        <f>IF(A195="","",N(H195)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A195))</f>
+        <v/>
+      </c>
+      <c r="L195" s="39">
+        <f>IF(A195="","",N(H195)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A195))</f>
+        <v/>
+      </c>
+      <c r="M195" s="39">
+        <f>IF(A195="","",IF(E195="Interno","Interno",IF(K195=0,"Sem horas",IF(L195&gt;N(F195),"Consome mais do que paga",IF(AND(N(G195)&gt;0,K195/G195&gt;1),"Estourou as horas",IF(AND(N(F195)&gt;0,(F195-L195)/F195&lt;0.2),"Margem baixa",IF(AND(N(G195)&gt;0,K195/G195&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="41" t="n"/>
@@ -9156,6 +11478,18 @@
       <c r="G196" s="46" t="n"/>
       <c r="H196" s="47" t="n"/>
       <c r="I196" s="42" t="n"/>
+      <c r="K196" s="39">
+        <f>IF(A196="","",N(H196)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A196))</f>
+        <v/>
+      </c>
+      <c r="L196" s="39">
+        <f>IF(A196="","",N(H196)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A196))</f>
+        <v/>
+      </c>
+      <c r="M196" s="39">
+        <f>IF(A196="","",IF(E196="Interno","Interno",IF(K196=0,"Sem horas",IF(L196&gt;N(F196),"Consome mais do que paga",IF(AND(N(G196)&gt;0,K196/G196&gt;1),"Estourou as horas",IF(AND(N(F196)&gt;0,(F196-L196)/F196&lt;0.2),"Margem baixa",IF(AND(N(G196)&gt;0,K196/G196&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="41" t="n"/>
@@ -9167,6 +11501,18 @@
       <c r="G197" s="46" t="n"/>
       <c r="H197" s="47" t="n"/>
       <c r="I197" s="42" t="n"/>
+      <c r="K197" s="39">
+        <f>IF(A197="","",N(H197)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A197))</f>
+        <v/>
+      </c>
+      <c r="L197" s="39">
+        <f>IF(A197="","",N(H197)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A197))</f>
+        <v/>
+      </c>
+      <c r="M197" s="39">
+        <f>IF(A197="","",IF(E197="Interno","Interno",IF(K197=0,"Sem horas",IF(L197&gt;N(F197),"Consome mais do que paga",IF(AND(N(G197)&gt;0,K197/G197&gt;1),"Estourou as horas",IF(AND(N(F197)&gt;0,(F197-L197)/F197&lt;0.2),"Margem baixa",IF(AND(N(G197)&gt;0,K197/G197&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="41" t="n"/>
@@ -9178,6 +11524,18 @@
       <c r="G198" s="46" t="n"/>
       <c r="H198" s="47" t="n"/>
       <c r="I198" s="42" t="n"/>
+      <c r="K198" s="39">
+        <f>IF(A198="","",N(H198)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A198))</f>
+        <v/>
+      </c>
+      <c r="L198" s="39">
+        <f>IF(A198="","",N(H198)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A198))</f>
+        <v/>
+      </c>
+      <c r="M198" s="39">
+        <f>IF(A198="","",IF(E198="Interno","Interno",IF(K198=0,"Sem horas",IF(L198&gt;N(F198),"Consome mais do que paga",IF(AND(N(G198)&gt;0,K198/G198&gt;1),"Estourou as horas",IF(AND(N(F198)&gt;0,(F198-L198)/F198&lt;0.2),"Margem baixa",IF(AND(N(G198)&gt;0,K198/G198&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="41" t="n"/>
@@ -9189,6 +11547,18 @@
       <c r="G199" s="46" t="n"/>
       <c r="H199" s="47" t="n"/>
       <c r="I199" s="42" t="n"/>
+      <c r="K199" s="39">
+        <f>IF(A199="","",N(H199)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A199))</f>
+        <v/>
+      </c>
+      <c r="L199" s="39">
+        <f>IF(A199="","",N(H199)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A199))</f>
+        <v/>
+      </c>
+      <c r="M199" s="39">
+        <f>IF(A199="","",IF(E199="Interno","Interno",IF(K199=0,"Sem horas",IF(L199&gt;N(F199),"Consome mais do que paga",IF(AND(N(G199)&gt;0,K199/G199&gt;1),"Estourou as horas",IF(AND(N(F199)&gt;0,(F199-L199)/F199&lt;0.2),"Margem baixa",IF(AND(N(G199)&gt;0,K199/G199&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="41" t="n"/>
@@ -9200,6 +11570,18 @@
       <c r="G200" s="46" t="n"/>
       <c r="H200" s="47" t="n"/>
       <c r="I200" s="42" t="n"/>
+      <c r="K200" s="39">
+        <f>IF(A200="","",N(H200)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A200))</f>
+        <v/>
+      </c>
+      <c r="L200" s="39">
+        <f>IF(A200="","",N(H200)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A200))</f>
+        <v/>
+      </c>
+      <c r="M200" s="39">
+        <f>IF(A200="","",IF(E200="Interno","Interno",IF(K200=0,"Sem horas",IF(L200&gt;N(F200),"Consome mais do que paga",IF(AND(N(G200)&gt;0,K200/G200&gt;1),"Estourou as horas",IF(AND(N(F200)&gt;0,(F200-L200)/F200&lt;0.2),"Margem baixa",IF(AND(N(G200)&gt;0,K200/G200&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="41" t="n"/>
@@ -9211,6 +11593,18 @@
       <c r="G201" s="46" t="n"/>
       <c r="H201" s="47" t="n"/>
       <c r="I201" s="42" t="n"/>
+      <c r="K201" s="39">
+        <f>IF(A201="","",N(H201)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A201))</f>
+        <v/>
+      </c>
+      <c r="L201" s="39">
+        <f>IF(A201="","",N(H201)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A201))</f>
+        <v/>
+      </c>
+      <c r="M201" s="39">
+        <f>IF(A201="","",IF(E201="Interno","Interno",IF(K201=0,"Sem horas",IF(L201&gt;N(F201),"Consome mais do que paga",IF(AND(N(G201)&gt;0,K201/G201&gt;1),"Estourou as horas",IF(AND(N(F201)&gt;0,(F201-L201)/F201&lt;0.2),"Margem baixa",IF(AND(N(G201)&gt;0,K201/G201&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="41" t="n"/>
@@ -9222,6 +11616,18 @@
       <c r="G202" s="46" t="n"/>
       <c r="H202" s="47" t="n"/>
       <c r="I202" s="42" t="n"/>
+      <c r="K202" s="39">
+        <f>IF(A202="","",N(H202)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A202))</f>
+        <v/>
+      </c>
+      <c r="L202" s="39">
+        <f>IF(A202="","",N(H202)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A202))</f>
+        <v/>
+      </c>
+      <c r="M202" s="39">
+        <f>IF(A202="","",IF(E202="Interno","Interno",IF(K202=0,"Sem horas",IF(L202&gt;N(F202),"Consome mais do que paga",IF(AND(N(G202)&gt;0,K202/G202&gt;1),"Estourou as horas",IF(AND(N(F202)&gt;0,(F202-L202)/F202&lt;0.2),"Margem baixa",IF(AND(N(G202)&gt;0,K202/G202&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="41" t="n"/>
@@ -9233,6 +11639,18 @@
       <c r="G203" s="46" t="n"/>
       <c r="H203" s="47" t="n"/>
       <c r="I203" s="42" t="n"/>
+      <c r="K203" s="39">
+        <f>IF(A203="","",N(H203)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A203))</f>
+        <v/>
+      </c>
+      <c r="L203" s="39">
+        <f>IF(A203="","",N(H203)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A203))</f>
+        <v/>
+      </c>
+      <c r="M203" s="39">
+        <f>IF(A203="","",IF(E203="Interno","Interno",IF(K203=0,"Sem horas",IF(L203&gt;N(F203),"Consome mais do que paga",IF(AND(N(G203)&gt;0,K203/G203&gt;1),"Estourou as horas",IF(AND(N(F203)&gt;0,(F203-L203)/F203&lt;0.2),"Margem baixa",IF(AND(N(G203)&gt;0,K203/G203&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="41" t="n"/>
@@ -9244,6 +11662,18 @@
       <c r="G204" s="46" t="n"/>
       <c r="H204" s="47" t="n"/>
       <c r="I204" s="42" t="n"/>
+      <c r="K204" s="39">
+        <f>IF(A204="","",N(H204)+SUMIFS(Lançamentos!$E$5:$E$604,Lançamentos!$C$5:$C$604,$A204))</f>
+        <v/>
+      </c>
+      <c r="L204" s="39">
+        <f>IF(A204="","",N(H204)*Config!$B$23+SUMIFS(Lançamentos!$H$5:$H$604,Lançamentos!$C$5:$C$604,$A204))</f>
+        <v/>
+      </c>
+      <c r="M204" s="39">
+        <f>IF(A204="","",IF(E204="Interno","Interno",IF(K204=0,"Sem horas",IF(L204&gt;N(F204),"Consome mais do que paga",IF(AND(N(G204)&gt;0,K204/G204&gt;1),"Estourou as horas",IF(AND(N(F204)&gt;0,(F204-L204)/F204&lt;0.2),"Margem baixa",IF(AND(N(G204)&gt;0,K204/G204&gt;0.85),"Perto do limite","Saudável")))))))</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="23" t="inlineStr">
@@ -9260,16 +11690,16 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D5:D204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$12,0,0,MAX(1,COUNTA(Config!$A$12:$A$21)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="E5:E204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$J$12,0,0,MAX(1,COUNTA(Config!$J$12:$J$21)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$H$12,0,0,MAX(1,COUNTA(Config!$H$12:$H$21)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:H204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5:H204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -29344,22 +31774,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="B5:B604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:B604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$12,0,0,MAX(1,COUNTA(Config!$A$12:$A$21)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Casos!$A$5,0,0,MAX(1,COUNTA(Casos!$A$5:$A$204)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$F$12,0,0,MAX(1,COUNTA(Config!$F$12:$F$23)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="F5:F604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E604" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="E5:E604" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>24</formula2>
     </dataValidation>
